--- a/Attendance Tabloid.xlsx
+++ b/Attendance Tabloid.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\butlemal\Desktop\PyTendance\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35783B2-D89B-4BC4-8168-3297E67081AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35115" yWindow="1545" windowWidth="21600" windowHeight="12645" firstSheet="10" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -30,22 +24,8 @@
     <sheet name="Week 14" sheetId="15" r:id="rId15"/>
     <sheet name="Week 15" sheetId="16" r:id="rId16"/>
     <sheet name="Total Labs Attended" sheetId="17" r:id="rId17"/>
-    <sheet name="Sheet1" sheetId="18" r:id="rId18"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -208,8 +188,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00%"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,7 +218,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
+        <fgColor rgb="FFFCE5CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -285,7 +268,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -296,7 +279,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFE599"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB7E1CD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -310,27 +300,12 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFFFE599"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -352,9 +327,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -392,7 +367,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -426,7 +401,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -461,10 +435,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -637,16 +610,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
     <col min="2" max="16" width="10.7109375" customWidth="1"/>
     <col min="17" max="17" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -699,7 +672,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -741,15 +714,15 @@
       </c>
       <c r="K2" s="2">
         <f>'Week 10'!G2</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="2">
         <f>'Week 11'!G2</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2">
         <f>'Week 12'!G2</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2">
         <f>'Week 13'!G2</f>
@@ -764,11 +737,11 @@
         <v>0</v>
       </c>
       <c r="Q2" s="2">
-        <f t="shared" ref="Q2:Q26" si="0">SUM(B2:P2)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B2:P2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -833,11 +806,11 @@
         <v>0</v>
       </c>
       <c r="Q3" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B3:P3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -902,11 +875,11 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B4:P4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
@@ -971,11 +944,11 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B5:P5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -1040,11 +1013,11 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B6:P6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -1109,11 +1082,11 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B7:P7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -1178,11 +1151,11 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B8:P8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -1247,11 +1220,11 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B9:P9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
@@ -1316,11 +1289,11 @@
         <v>0</v>
       </c>
       <c r="Q10" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B10:P10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -1385,11 +1358,11 @@
         <v>0</v>
       </c>
       <c r="Q11" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B11:P11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="2" t="s">
         <v>27</v>
       </c>
@@ -1454,11 +1427,11 @@
         <v>0</v>
       </c>
       <c r="Q12" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B12:P12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
@@ -1523,11 +1496,11 @@
         <v>0</v>
       </c>
       <c r="Q13" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B13:P13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
@@ -1592,11 +1565,11 @@
         <v>0</v>
       </c>
       <c r="Q14" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B14:P14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
         <v>30</v>
       </c>
@@ -1661,11 +1634,11 @@
         <v>0</v>
       </c>
       <c r="Q15" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B15:P15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
@@ -1730,11 +1703,11 @@
         <v>0</v>
       </c>
       <c r="Q16" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B16:P16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
@@ -1799,11 +1772,11 @@
         <v>0</v>
       </c>
       <c r="Q17" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B17:P17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="2" t="s">
         <v>33</v>
       </c>
@@ -1868,11 +1841,11 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B18:P18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="2" t="s">
         <v>34</v>
       </c>
@@ -1937,11 +1910,11 @@
         <v>0</v>
       </c>
       <c r="Q19" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B19:P19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="2" t="s">
         <v>35</v>
       </c>
@@ -2006,11 +1979,11 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B20:P20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="2" t="s">
         <v>36</v>
       </c>
@@ -2075,11 +2048,11 @@
         <v>0</v>
       </c>
       <c r="Q21" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B21:P21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="2" t="s">
         <v>37</v>
       </c>
@@ -2144,11 +2117,11 @@
         <v>0</v>
       </c>
       <c r="Q22" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B22:P22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" s="2" t="s">
         <v>38</v>
       </c>
@@ -2213,11 +2186,11 @@
         <v>0</v>
       </c>
       <c r="Q23" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B23:P23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24" s="2" t="s">
         <v>39</v>
       </c>
@@ -2282,11 +2255,11 @@
         <v>0</v>
       </c>
       <c r="Q24" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B24:P24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25" s="2" t="s">
         <v>40</v>
       </c>
@@ -2351,11 +2324,11 @@
         <v>0</v>
       </c>
       <c r="Q25" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B25:P25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26" s="2" t="s">
         <v>41</v>
       </c>
@@ -2420,23 +2393,23 @@
         <v>0</v>
       </c>
       <c r="Q26" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(B26:P26)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:P26">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>1</formula>
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2445,9 +2418,9 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -2457,7 +2430,7 @@
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2480,7 +2453,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -2497,15 +2470,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -2522,15 +2495,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -2547,15 +2520,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -2572,15 +2545,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -2597,15 +2570,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2622,15 +2595,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -2647,15 +2620,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2672,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -2697,15 +2670,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -2722,15 +2695,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -2747,15 +2720,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2772,15 +2745,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -2797,15 +2770,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2822,15 +2795,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -2847,15 +2820,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -2872,15 +2845,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -2897,15 +2870,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -2922,15 +2895,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -2947,15 +2920,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -2972,15 +2945,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -2997,15 +2970,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -3022,15 +2995,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -3047,15 +3020,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -3072,15 +3045,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -3097,11 +3070,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3111,9 +3084,9 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -3123,7 +3096,7 @@
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3146,7 +3119,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -3154,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3" t="b">
         <v>0</v>
@@ -3163,15 +3136,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
-        <v>1</v>
+        <f>COUNTIF(B2:E2, TRUE)</f>
+        <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3188,15 +3161,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -3213,15 +3186,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -3238,15 +3211,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -3263,15 +3236,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3288,15 +3261,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -3313,15 +3286,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -3338,15 +3311,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -3363,15 +3336,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -3388,15 +3361,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -3413,15 +3386,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -3438,15 +3411,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -3463,15 +3436,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -3488,15 +3461,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -3513,15 +3486,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3538,15 +3511,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -3563,15 +3536,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -3588,15 +3561,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -3613,15 +3586,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -3638,15 +3611,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -3663,15 +3636,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -3688,15 +3661,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -3713,15 +3686,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -3738,15 +3711,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -3763,11 +3736,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3777,9 +3750,9 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -3789,7 +3762,7 @@
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3812,7 +3785,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -3820,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3" t="b">
         <v>0</v>
@@ -3829,15 +3802,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
-        <v>1</v>
+        <f>COUNTIF(B2:E2, TRUE)</f>
+        <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3854,15 +3827,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -3879,15 +3852,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -3904,15 +3877,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -3929,15 +3902,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3954,15 +3927,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -3979,15 +3952,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -4004,15 +3977,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -4029,15 +4002,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -4054,15 +4027,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -4079,15 +4052,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -4104,15 +4077,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -4129,15 +4102,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -4154,15 +4127,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -4179,15 +4152,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -4204,15 +4177,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -4229,15 +4202,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -4254,15 +4227,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -4279,15 +4252,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -4304,15 +4277,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -4329,15 +4302,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -4354,15 +4327,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -4379,15 +4352,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -4404,15 +4377,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -4429,11 +4402,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -4443,9 +4416,9 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -4455,7 +4428,7 @@
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4478,7 +4451,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -4486,7 +4459,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3" t="b">
         <v>0</v>
@@ -4495,15 +4468,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
-        <v>1</v>
+        <f>COUNTIF(B2:E2, TRUE)</f>
+        <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -4520,15 +4493,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -4545,15 +4518,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -4570,15 +4543,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -4595,15 +4568,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -4620,15 +4593,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -4645,15 +4618,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -4670,15 +4643,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -4695,15 +4668,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -4720,15 +4693,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -4745,15 +4718,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -4770,15 +4743,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -4795,15 +4768,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -4820,15 +4793,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -4845,15 +4818,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -4870,15 +4843,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -4895,15 +4868,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -4920,15 +4893,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -4945,15 +4918,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -4970,15 +4943,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -4995,15 +4968,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -5020,15 +4993,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -5045,15 +5018,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -5070,15 +5043,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -5095,11 +5068,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -5109,9 +5082,9 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -5121,7 +5094,7 @@
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5144,7 +5117,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -5161,15 +5134,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -5186,15 +5159,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -5211,15 +5184,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -5236,15 +5209,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -5261,15 +5234,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -5286,15 +5259,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -5311,15 +5284,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -5336,15 +5309,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -5361,15 +5334,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -5386,15 +5359,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -5411,15 +5384,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -5436,15 +5409,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -5461,15 +5434,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -5486,15 +5459,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -5511,15 +5484,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -5536,15 +5509,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -5561,15 +5534,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -5586,15 +5559,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -5611,15 +5584,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -5636,15 +5609,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -5661,15 +5634,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -5686,15 +5659,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -5711,15 +5684,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -5736,15 +5709,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -5761,11 +5734,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -5775,9 +5748,9 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -5787,7 +5760,7 @@
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5810,7 +5783,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -5827,15 +5800,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -5852,15 +5825,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -5877,15 +5850,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -5902,15 +5875,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -5927,15 +5900,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -5952,15 +5925,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -5977,15 +5950,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -6002,15 +5975,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -6027,15 +6000,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -6052,15 +6025,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -6077,15 +6050,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -6102,15 +6075,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -6127,15 +6100,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -6152,15 +6125,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -6177,15 +6150,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -6202,15 +6175,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -6227,15 +6200,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -6252,15 +6225,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -6277,15 +6250,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -6302,15 +6275,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -6327,15 +6300,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -6352,15 +6325,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -6377,15 +6350,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -6402,15 +6375,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -6427,11 +6400,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -6441,9 +6414,9 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -6453,7 +6426,7 @@
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -6476,7 +6449,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -6493,15 +6466,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -6518,15 +6491,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -6543,15 +6516,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -6568,15 +6541,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -6593,15 +6566,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -6618,15 +6591,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -6643,15 +6616,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -6668,15 +6641,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -6693,15 +6666,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -6718,15 +6691,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -6743,15 +6716,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -6768,15 +6741,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -6793,15 +6766,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -6818,15 +6791,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -6843,15 +6816,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -6868,15 +6841,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -6893,15 +6866,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -6918,15 +6891,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -6943,15 +6916,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -6968,15 +6941,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -6993,15 +6966,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -7018,15 +6991,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -7043,15 +7016,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -7068,15 +7041,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -7093,11 +7066,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -7107,14 +7080,14 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -7125,20 +7098,20 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="4">
         <f>SUM('Week 1:Week 15'!H2)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C2" s="5">
         <f>SUM('Week 1:Week 15'!H2) / 16</f>
-        <v>0.1875</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -7151,7 +7124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -7164,7 +7137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -7177,7 +7150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -7190,7 +7163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -7203,7 +7176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -7216,7 +7189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -7229,7 +7202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -7242,7 +7215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -7255,7 +7228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -7268,7 +7241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -7281,7 +7254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -7294,7 +7267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -7307,7 +7280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -7320,7 +7293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -7333,7 +7306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -7346,7 +7319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -7359,7 +7332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -7372,7 +7345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -7385,7 +7358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -7398,7 +7371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -7411,7 +7384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -7424,7 +7397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -7437,7 +7410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -7455,19 +7428,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{600B6E1E-255D-40B9-8964-BA24EA410A8D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -7477,7 +7441,7 @@
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -7500,7 +7464,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -7517,15 +7481,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -7542,15 +7506,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -7567,15 +7531,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -7592,15 +7556,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -7617,15 +7581,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -7642,15 +7606,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -7667,15 +7631,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -7692,15 +7656,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -7717,15 +7681,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -7742,15 +7706,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -7767,15 +7731,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -7792,15 +7756,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -7817,15 +7781,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -7842,15 +7806,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -7867,15 +7831,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -7892,15 +7856,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -7917,15 +7881,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -7942,15 +7906,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -7967,15 +7931,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -7992,15 +7956,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -8017,15 +7981,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -8042,15 +8006,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -8067,15 +8031,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -8092,15 +8056,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -8117,11 +8081,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -8131,9 +8095,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -8143,7 +8107,7 @@
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -8166,7 +8130,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -8183,15 +8147,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -8208,15 +8172,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -8233,15 +8197,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -8258,15 +8222,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -8283,15 +8247,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -8308,15 +8272,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -8333,15 +8297,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -8358,15 +8322,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -8383,15 +8347,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -8408,15 +8372,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -8433,15 +8397,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -8458,15 +8422,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -8483,15 +8447,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -8508,15 +8472,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -8533,15 +8497,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -8558,15 +8522,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -8583,15 +8547,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -8608,15 +8572,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -8633,15 +8597,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -8658,15 +8622,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -8683,15 +8647,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -8708,15 +8672,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -8733,15 +8697,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -8758,15 +8722,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -8783,11 +8747,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -8797,9 +8761,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -8809,7 +8773,7 @@
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -8832,7 +8796,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -8849,15 +8813,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -8874,15 +8838,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -8899,15 +8863,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -8924,15 +8888,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -8949,15 +8913,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -8974,15 +8938,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -8999,15 +8963,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -9024,15 +8988,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -9049,15 +9013,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -9074,15 +9038,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -9099,15 +9063,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -9124,15 +9088,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -9149,15 +9113,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -9174,15 +9138,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -9199,15 +9163,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -9224,15 +9188,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -9249,15 +9213,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -9274,15 +9238,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -9299,15 +9263,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -9324,15 +9288,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -9349,15 +9313,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -9374,15 +9338,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -9399,15 +9363,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -9424,15 +9388,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -9449,11 +9413,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -9463,9 +9427,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -9475,7 +9439,7 @@
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -9498,7 +9462,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -9515,15 +9479,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -9540,15 +9504,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -9565,15 +9529,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -9590,15 +9554,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -9615,15 +9579,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -9640,15 +9604,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -9665,15 +9629,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -9690,15 +9654,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -9715,15 +9679,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -9740,15 +9704,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -9765,15 +9729,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -9790,15 +9754,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -9815,15 +9779,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -9840,15 +9804,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -9865,15 +9829,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -9890,15 +9854,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -9915,15 +9879,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -9940,15 +9904,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -9965,15 +9929,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -9990,15 +9954,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -10015,15 +9979,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -10040,15 +10004,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -10065,15 +10029,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -10090,15 +10054,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -10115,11 +10079,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -10129,9 +10093,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -10141,7 +10105,7 @@
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -10164,7 +10128,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -10181,15 +10145,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -10206,15 +10170,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -10231,15 +10195,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -10256,15 +10220,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -10281,15 +10245,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -10306,15 +10270,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -10331,15 +10295,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -10356,15 +10320,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -10381,15 +10345,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -10406,15 +10370,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -10431,15 +10395,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -10456,15 +10420,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -10481,15 +10445,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -10506,15 +10470,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -10531,15 +10495,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -10556,15 +10520,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -10581,15 +10545,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -10606,15 +10570,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -10631,15 +10595,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -10656,15 +10620,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -10681,15 +10645,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -10706,15 +10670,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -10731,15 +10695,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -10756,15 +10720,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -10781,11 +10745,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -10795,9 +10759,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -10807,7 +10771,7 @@
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -10830,7 +10794,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -10847,15 +10811,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -10872,15 +10836,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -10897,15 +10861,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -10922,15 +10886,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -10947,15 +10911,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -10972,15 +10936,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -10997,15 +10961,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -11022,15 +10986,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -11047,15 +11011,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -11072,15 +11036,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -11097,15 +11061,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -11122,15 +11086,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -11147,15 +11111,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -11172,15 +11136,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -11197,15 +11161,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -11222,15 +11186,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -11247,15 +11211,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -11272,15 +11236,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -11297,15 +11261,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -11322,15 +11286,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -11347,15 +11311,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -11372,15 +11336,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -11397,15 +11361,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -11422,15 +11386,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -11447,11 +11411,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -11461,9 +11425,9 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -11473,7 +11437,7 @@
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -11496,7 +11460,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -11513,15 +11477,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -11538,15 +11502,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -11563,15 +11527,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -11588,15 +11552,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -11613,15 +11577,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -11638,15 +11602,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -11663,15 +11627,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -11688,15 +11652,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -11713,15 +11677,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -11738,15 +11702,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -11763,15 +11727,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -11788,15 +11752,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -11813,15 +11777,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -11838,15 +11802,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -11863,15 +11827,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -11888,15 +11852,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -11913,15 +11877,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -11938,15 +11902,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -11963,15 +11927,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -11988,15 +11952,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -12013,15 +11977,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -12038,15 +12002,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -12063,15 +12027,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -12088,15 +12052,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -12113,11 +12077,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -12127,9 +12091,9 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -12139,7 +12103,7 @@
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -12162,7 +12126,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -12179,15 +12143,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -12204,15 +12168,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -12229,15 +12193,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -12254,15 +12218,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -12279,15 +12243,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -12304,15 +12268,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -12329,15 +12293,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -12354,15 +12318,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -12379,15 +12343,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -12404,15 +12368,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -12429,15 +12393,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -12454,15 +12418,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -12479,15 +12443,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -12504,15 +12468,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -12529,15 +12493,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -12554,15 +12518,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -12579,15 +12543,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -12604,15 +12568,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -12629,15 +12593,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -12654,15 +12618,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -12679,15 +12643,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -12704,15 +12668,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -12729,15 +12693,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -12754,15 +12718,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -12779,11 +12743,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>

--- a/Attendance Tabloid.xlsx
+++ b/Attendance Tabloid.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="49">
   <si>
     <t>Name</t>
   </si>
@@ -81,9 +81,6 @@
   </si>
   <si>
     <t>Total Attended</t>
-  </si>
-  <si>
-    <t>Adegoke, Olusegun</t>
   </si>
   <si>
     <t>Adeleye, Rasheed</t>
@@ -141,9 +138,6 @@
   </si>
   <si>
     <t>Mellado Ostolaza, Johnny</t>
-  </si>
-  <si>
-    <t>Miller, Gavin</t>
   </si>
   <si>
     <t>Navarrete, Bryant</t>
@@ -218,7 +212,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE5CD"/>
+        <fgColor rgb="FFE6B8AF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,7 +605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -2259,146 +2253,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
-      <c r="A25" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="2">
-        <f>'Week 1'!G25</f>
-        <v>0</v>
-      </c>
-      <c r="C25" s="2">
-        <f>'Week 2'!G25</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="2">
-        <f>'Week 3'!G25</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="2">
-        <f>'Week 4'!G25</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="2">
-        <f>'Week 5'!G25</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="2">
-        <f>'Week 6'!G25</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="2">
-        <f>'Week 7'!G25</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="2">
-        <f>'Week 8'!G25</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="2">
-        <f>'Week 9'!G25</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="2">
-        <f>'Week 10'!G25</f>
-        <v>0</v>
-      </c>
-      <c r="L25" s="2">
-        <f>'Week 11'!G25</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="2">
-        <f>'Week 12'!G25</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="2">
-        <f>'Week 13'!G25</f>
-        <v>0</v>
-      </c>
-      <c r="O25" s="2">
-        <f>'Week 14'!G25</f>
-        <v>0</v>
-      </c>
-      <c r="P25" s="2">
-        <f>'Week 15'!G25</f>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="2">
-        <f>SUM(B25:P25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17">
-      <c r="A26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="2">
-        <f>'Week 1'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="C26" s="2">
-        <f>'Week 2'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="2">
-        <f>'Week 3'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="2">
-        <f>'Week 4'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="2">
-        <f>'Week 5'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="2">
-        <f>'Week 6'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="2">
-        <f>'Week 7'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <f>'Week 8'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="2">
-        <f>'Week 9'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="2">
-        <f>'Week 10'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="L26" s="2">
-        <f>'Week 11'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="M26" s="2">
-        <f>'Week 12'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="N26" s="2">
-        <f>'Week 13'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="O26" s="2">
-        <f>'Week 14'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="P26" s="2">
-        <f>'Week 15'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="2">
-        <f>SUM(B26:P26)</f>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P26">
+  <conditionalFormatting sqref="B2:P24">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -2419,7 +2275,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -2432,25 +2288,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2466,9 +2322,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -2491,9 +2344,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -2516,9 +2366,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -2541,9 +2388,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -2566,9 +2410,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -2591,9 +2432,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -2616,9 +2454,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -2641,9 +2476,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -2666,9 +2498,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -2691,9 +2520,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -2716,9 +2542,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -2741,9 +2564,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -2766,9 +2586,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -2791,9 +2608,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -2816,9 +2630,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -2841,9 +2652,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -2866,9 +2674,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -2891,9 +2696,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -2916,9 +2718,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -2941,9 +2740,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -2966,9 +2762,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -2991,9 +2784,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -3016,65 +2806,12 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f>COUNTIF(B25:E25, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4">
-        <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3085,7 +2822,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -3098,25 +2835,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3132,9 +2869,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -3157,9 +2891,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -3182,9 +2913,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -3207,9 +2935,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -3232,9 +2957,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -3257,9 +2979,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -3282,9 +3001,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -3307,9 +3023,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -3332,9 +3045,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -3357,9 +3067,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -3382,9 +3089,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -3407,9 +3111,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -3432,9 +3133,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -3457,9 +3155,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -3482,9 +3177,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -3507,9 +3199,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -3532,9 +3221,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -3557,9 +3243,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -3582,9 +3265,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -3607,9 +3287,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -3632,9 +3309,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -3657,9 +3331,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -3682,65 +3353,12 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f>COUNTIF(B25:E25, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4">
-        <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3751,7 +3369,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -3764,25 +3382,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3798,9 +3416,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -3823,9 +3438,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -3848,9 +3460,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -3873,9 +3482,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -3898,9 +3504,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -3923,9 +3526,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -3948,9 +3548,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -3973,9 +3570,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -3998,9 +3592,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -4023,9 +3614,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -4048,9 +3636,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -4073,9 +3658,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -4098,9 +3680,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -4123,9 +3702,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -4148,9 +3724,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -4173,9 +3746,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -4198,9 +3768,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -4223,9 +3790,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -4248,9 +3812,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -4273,9 +3834,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -4298,9 +3856,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -4323,9 +3878,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -4348,65 +3900,12 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f>COUNTIF(B25:E25, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4">
-        <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -4417,7 +3916,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -4430,25 +3929,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4464,9 +3963,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -4489,9 +3985,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -4514,9 +4007,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -4539,9 +4029,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -4564,9 +4051,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -4589,9 +4073,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -4614,9 +4095,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -4639,9 +4117,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -4664,9 +4139,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -4689,9 +4161,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -4714,9 +4183,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -4739,9 +4205,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -4764,9 +4227,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -4789,9 +4249,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -4814,9 +4271,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -4839,9 +4293,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -4864,9 +4315,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -4889,9 +4337,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -4914,9 +4359,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -4939,9 +4381,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -4964,9 +4403,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -4989,9 +4425,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -5014,65 +4447,12 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f>COUNTIF(B25:E25, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4">
-        <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -5083,7 +4463,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -5096,25 +4476,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5130,9 +4510,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -5155,9 +4532,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -5180,9 +4554,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -5205,9 +4576,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -5230,9 +4598,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -5255,9 +4620,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -5280,9 +4642,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -5305,9 +4664,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -5330,9 +4686,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -5355,9 +4708,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -5380,9 +4730,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -5405,9 +4752,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -5430,9 +4774,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -5455,9 +4796,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -5480,9 +4818,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -5505,9 +4840,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -5530,9 +4862,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -5555,9 +4884,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -5580,9 +4906,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -5605,9 +4928,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -5630,9 +4950,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -5655,9 +4972,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -5680,65 +4994,12 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f>COUNTIF(B25:E25, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4">
-        <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -5749,7 +5010,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -5762,25 +5023,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5796,9 +5057,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -5821,9 +5079,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -5846,9 +5101,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -5871,9 +5123,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -5896,9 +5145,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -5921,9 +5167,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -5946,9 +5189,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -5971,9 +5211,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -5996,9 +5233,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -6021,9 +5255,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -6046,9 +5277,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -6071,9 +5299,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -6096,9 +5321,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -6121,9 +5343,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -6146,9 +5365,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -6171,9 +5387,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -6196,9 +5409,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -6221,9 +5431,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -6246,9 +5453,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -6271,9 +5475,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -6296,9 +5497,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -6321,9 +5519,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -6346,65 +5541,12 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f>COUNTIF(B25:E25, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4">
-        <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -6415,7 +5557,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -6428,25 +5570,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6462,9 +5604,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -6487,9 +5626,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -6512,9 +5648,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -6537,9 +5670,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -6562,9 +5692,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -6587,9 +5714,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -6612,9 +5736,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -6637,9 +5758,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -6662,9 +5780,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -6687,9 +5802,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -6712,9 +5824,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -6737,9 +5846,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -6762,9 +5868,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -6787,9 +5890,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -6812,9 +5912,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -6837,9 +5934,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -6862,9 +5956,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -6887,9 +5978,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -6912,9 +6000,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -6937,9 +6022,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -6962,9 +6044,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -6987,9 +6066,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -7012,65 +6088,12 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f>COUNTIF(B25:E25, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4">
-        <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -7081,7 +6104,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -7089,13 +6112,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -7394,32 +6417,6 @@
       </c>
       <c r="C24" s="5">
         <f>SUM('Week 1:Week 15'!H24) / 16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="4">
-        <f>SUM('Week 1:Week 15'!H25)</f>
-        <v>0</v>
-      </c>
-      <c r="C25" s="5">
-        <f>SUM('Week 1:Week 15'!H25) / 16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="4">
-        <f>SUM('Week 1:Week 15'!H26)</f>
-        <v>0</v>
-      </c>
-      <c r="C26" s="5">
-        <f>SUM('Week 1:Week 15'!H26) / 16</f>
         <v>0</v>
       </c>
     </row>
@@ -7430,7 +6427,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -7443,25 +6440,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7475,10 +6472,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
@@ -7494,15 +6488,12 @@
         <v>18</v>
       </c>
       <c r="B3" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="b">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="b">
         <v>0</v>
       </c>
       <c r="G3" s="4">
@@ -7527,9 +6518,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -7547,12 +6535,9 @@
         <v>0</v>
       </c>
       <c r="C5" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="b">
         <v>0</v>
       </c>
       <c r="G5" s="4">
@@ -7577,9 +6562,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -7602,9 +6584,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -7622,12 +6601,9 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="b">
         <v>0</v>
       </c>
       <c r="G8" s="4">
@@ -7652,9 +6628,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -7677,9 +6650,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -7702,9 +6672,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -7727,9 +6694,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -7752,9 +6716,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -7777,9 +6738,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -7802,9 +6760,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -7827,9 +6782,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -7852,9 +6804,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -7877,9 +6826,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -7902,9 +6848,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -7927,9 +6870,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -7944,15 +6884,12 @@
         <v>36</v>
       </c>
       <c r="B21" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3" t="b">
         <v>0</v>
       </c>
       <c r="G21" s="4">
@@ -7977,9 +6914,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -8002,9 +6936,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -8027,65 +6958,12 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f>COUNTIF(B25:E25, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4">
-        <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -8096,7 +6974,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -8109,25 +6987,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8143,9 +7021,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -8168,9 +7043,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -8193,9 +7065,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -8218,9 +7087,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -8243,9 +7109,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -8268,9 +7131,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -8293,9 +7153,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -8318,9 +7175,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -8343,9 +7197,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -8368,9 +7219,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -8393,9 +7241,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -8418,9 +7263,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -8443,9 +7285,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -8468,9 +7307,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -8493,9 +7329,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -8518,9 +7351,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -8543,9 +7373,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -8568,9 +7395,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -8593,9 +7417,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -8618,9 +7439,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -8643,9 +7461,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -8668,9 +7483,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -8693,65 +7505,12 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f>COUNTIF(B25:E25, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4">
-        <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -8762,7 +7521,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -8775,25 +7534,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8809,9 +7568,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -8834,9 +7590,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -8859,9 +7612,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -8884,9 +7634,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -8909,9 +7656,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -8934,9 +7678,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -8959,9 +7700,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -8984,9 +7722,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -9009,9 +7744,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -9034,9 +7766,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -9059,9 +7788,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -9084,9 +7810,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -9109,9 +7832,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -9134,9 +7854,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -9159,9 +7876,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -9184,9 +7898,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -9209,9 +7920,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -9234,9 +7942,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -9259,9 +7964,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -9284,9 +7986,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -9309,9 +8008,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -9334,9 +8030,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -9359,65 +8052,12 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f>COUNTIF(B25:E25, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4">
-        <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -9428,7 +8068,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -9441,25 +8081,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -9475,9 +8115,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -9500,9 +8137,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -9525,9 +8159,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -9550,9 +8181,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -9575,9 +8203,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -9600,9 +8225,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -9625,9 +8247,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -9650,9 +8269,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -9675,9 +8291,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -9700,9 +8313,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -9725,9 +8335,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -9750,9 +8357,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -9775,9 +8379,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -9800,9 +8401,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -9825,9 +8423,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -9850,9 +8445,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -9875,9 +8467,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -9900,9 +8489,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -9925,9 +8511,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -9950,9 +8533,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -9975,9 +8555,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -10000,9 +8577,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -10025,65 +8599,12 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f>COUNTIF(B25:E25, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4">
-        <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -10094,7 +8615,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -10107,25 +8628,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -10141,9 +8662,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -10166,9 +8684,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -10191,9 +8706,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -10216,9 +8728,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -10241,9 +8750,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -10266,9 +8772,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -10291,9 +8794,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -10316,9 +8816,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -10341,9 +8838,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -10366,9 +8860,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -10391,9 +8882,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -10416,9 +8904,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -10441,9 +8926,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -10466,9 +8948,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -10491,9 +8970,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -10516,9 +8992,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -10541,9 +9014,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -10566,9 +9036,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -10591,9 +9058,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -10616,9 +9080,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -10641,9 +9102,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -10666,9 +9124,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -10691,65 +9146,12 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f>COUNTIF(B25:E25, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4">
-        <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -10760,7 +9162,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -10773,25 +9175,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -10807,9 +9209,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -10832,9 +9231,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -10857,9 +9253,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -10882,9 +9275,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -10907,9 +9297,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -10932,9 +9319,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -10957,9 +9341,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -10982,9 +9363,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -11007,9 +9385,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -11032,9 +9407,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -11057,9 +9429,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -11082,9 +9451,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -11107,9 +9473,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -11132,9 +9495,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -11157,9 +9517,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -11182,9 +9539,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -11207,9 +9561,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -11232,9 +9583,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -11257,9 +9605,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -11282,9 +9627,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -11307,9 +9649,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -11332,9 +9671,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -11357,65 +9693,12 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f>COUNTIF(B25:E25, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4">
-        <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -11426,7 +9709,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -11439,25 +9722,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -11473,9 +9756,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -11498,9 +9778,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -11523,9 +9800,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -11548,9 +9822,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -11573,9 +9844,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -11598,9 +9866,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -11623,9 +9888,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -11648,9 +9910,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -11673,9 +9932,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -11698,9 +9954,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -11723,9 +9976,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -11748,9 +9998,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -11773,9 +10020,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -11798,9 +10042,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -11823,9 +10064,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -11848,9 +10086,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -11873,9 +10108,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -11898,9 +10130,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -11923,9 +10152,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -11948,9 +10174,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -11973,9 +10196,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -11998,9 +10218,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -12023,65 +10240,12 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f>COUNTIF(B25:E25, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4">
-        <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -12092,7 +10256,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -12105,25 +10269,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -12139,9 +10303,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -12164,9 +10325,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -12189,9 +10347,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -12214,9 +10369,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -12239,9 +10391,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -12264,9 +10413,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -12289,9 +10435,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -12314,9 +10457,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -12339,9 +10479,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -12364,9 +10501,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -12389,9 +10523,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -12414,9 +10545,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -12439,9 +10567,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -12464,9 +10589,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -12489,9 +10611,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -12514,9 +10633,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -12539,9 +10655,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -12564,9 +10677,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -12589,9 +10699,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -12614,9 +10721,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -12639,9 +10743,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -12664,9 +10765,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -12689,65 +10787,12 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
-        <f>COUNTIF(B25:E25, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4">
-        <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>

--- a/Attendance Tabloid.xlsx
+++ b/Attendance Tabloid.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="51">
   <si>
     <t>Name</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>Total Attended</t>
+  </si>
+  <si>
+    <t>Adegoke, Olusegun</t>
   </si>
   <si>
     <t>Adeleye, Rasheed</t>
@@ -138,6 +141,9 @@
   </si>
   <si>
     <t>Mellado Ostolaza, Johnny</t>
+  </si>
+  <si>
+    <t>Miller, Gavin</t>
   </si>
   <si>
     <t>Navarrete, Bryant</t>
@@ -212,7 +218,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6B8AF"/>
+        <fgColor rgb="FFC9DAF8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -605,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -2253,8 +2259,146 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="2">
+        <f>'Week 1'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <f>'Week 2'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <f>'Week 3'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <f>'Week 4'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <f>'Week 5'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <f>'Week 6'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <f>'Week 7'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <f>'Week 8'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
+        <f>'Week 9'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="2">
+        <f>'Week 10'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="2">
+        <f>'Week 11'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="2">
+        <f>'Week 12'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="N25" s="2">
+        <f>'Week 13'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="2">
+        <f>'Week 14'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="2">
+        <f>'Week 15'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2">
+        <f>SUM(B25:P25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="2">
+        <f>'Week 1'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
+        <f>'Week 2'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <f>'Week 3'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <f>'Week 4'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="2">
+        <f>'Week 5'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="2">
+        <f>'Week 6'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="2">
+        <f>'Week 7'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <f>'Week 8'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
+        <f>'Week 9'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="2">
+        <f>'Week 10'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="2">
+        <f>'Week 11'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="2">
+        <f>'Week 12'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="2">
+        <f>'Week 13'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="O26" s="2">
+        <f>'Week 14'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="P26" s="2">
+        <f>'Week 15'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2">
+        <f>SUM(B26:P26)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P24">
+  <conditionalFormatting sqref="B2:P26">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -2275,7 +2419,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -2288,25 +2432,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2322,6 +2466,9 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -2344,6 +2491,9 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -2366,6 +2516,9 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -2388,6 +2541,9 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -2410,6 +2566,9 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -2432,6 +2591,9 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -2454,6 +2616,9 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -2476,6 +2641,9 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -2498,6 +2666,9 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -2520,6 +2691,9 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -2542,6 +2716,9 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -2564,6 +2741,9 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -2586,6 +2766,9 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -2608,6 +2791,9 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -2630,6 +2816,9 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -2652,6 +2841,9 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E17" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -2674,6 +2866,9 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -2696,6 +2891,9 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -2718,6 +2916,9 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -2740,6 +2941,9 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -2762,6 +2966,9 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -2784,6 +2991,9 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E23" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -2806,12 +3016,65 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E24" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>COUNTIF(B26:E26, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -2822,7 +3085,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -2835,25 +3098,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2869,6 +3132,9 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -2891,6 +3157,9 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -2913,6 +3182,9 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -2935,6 +3207,9 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -2957,6 +3232,9 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -2979,6 +3257,9 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -3001,6 +3282,9 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -3023,6 +3307,9 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -3045,6 +3332,9 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -3067,6 +3357,9 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -3089,6 +3382,9 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -3111,6 +3407,9 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -3133,6 +3432,9 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -3155,6 +3457,9 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -3177,6 +3482,9 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -3199,6 +3507,9 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E17" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -3221,6 +3532,9 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -3243,6 +3557,9 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -3265,6 +3582,9 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -3287,6 +3607,9 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -3309,6 +3632,9 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -3331,6 +3657,9 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E23" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -3353,12 +3682,65 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E24" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>COUNTIF(B26:E26, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3369,7 +3751,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -3382,25 +3764,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3416,6 +3798,9 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -3438,6 +3823,9 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -3460,6 +3848,9 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -3482,6 +3873,9 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -3504,6 +3898,9 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -3526,6 +3923,9 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -3548,6 +3948,9 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -3570,6 +3973,9 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -3592,6 +3998,9 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -3614,6 +4023,9 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -3636,6 +4048,9 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -3658,6 +4073,9 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -3680,6 +4098,9 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -3702,6 +4123,9 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -3724,6 +4148,9 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -3746,6 +4173,9 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E17" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -3768,6 +4198,9 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -3790,6 +4223,9 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -3812,6 +4248,9 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -3834,6 +4273,9 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -3856,6 +4298,9 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -3878,6 +4323,9 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E23" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -3900,12 +4348,65 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E24" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>COUNTIF(B26:E26, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3916,7 +4417,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -3929,25 +4430,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3963,6 +4464,9 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -3985,6 +4489,9 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -4007,6 +4514,9 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -4029,6 +4539,9 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -4051,6 +4564,9 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -4073,6 +4589,9 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -4095,6 +4614,9 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -4117,6 +4639,9 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -4139,6 +4664,9 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -4161,6 +4689,9 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -4183,6 +4714,9 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -4205,6 +4739,9 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -4227,6 +4764,9 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -4249,6 +4789,9 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -4271,6 +4814,9 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -4293,6 +4839,9 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E17" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -4315,6 +4864,9 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -4337,6 +4889,9 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -4359,6 +4914,9 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -4381,6 +4939,9 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -4403,6 +4964,9 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -4425,6 +4989,9 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E23" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -4447,12 +5014,65 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E24" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>COUNTIF(B26:E26, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -4463,7 +5083,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -4476,25 +5096,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4510,6 +5130,9 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -4532,6 +5155,9 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -4554,6 +5180,9 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -4576,6 +5205,9 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -4598,6 +5230,9 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -4620,6 +5255,9 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -4642,6 +5280,9 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -4664,6 +5305,9 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -4686,6 +5330,9 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -4708,6 +5355,9 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -4730,6 +5380,9 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -4752,6 +5405,9 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -4774,6 +5430,9 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -4796,6 +5455,9 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -4818,6 +5480,9 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -4840,6 +5505,9 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E17" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -4862,6 +5530,9 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -4884,6 +5555,9 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -4906,6 +5580,9 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -4928,6 +5605,9 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -4950,6 +5630,9 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -4972,6 +5655,9 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E23" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -4994,12 +5680,65 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E24" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>COUNTIF(B26:E26, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -5010,7 +5749,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -5023,25 +5762,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5057,6 +5796,9 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -5079,6 +5821,9 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -5101,6 +5846,9 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -5123,6 +5871,9 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -5145,6 +5896,9 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -5167,6 +5921,9 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -5189,6 +5946,9 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -5211,6 +5971,9 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -5233,6 +5996,9 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -5255,6 +6021,9 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -5277,6 +6046,9 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -5299,6 +6071,9 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -5321,6 +6096,9 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -5343,6 +6121,9 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -5365,6 +6146,9 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -5387,6 +6171,9 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E17" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -5409,6 +6196,9 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -5431,6 +6221,9 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -5453,6 +6246,9 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -5475,6 +6271,9 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -5497,6 +6296,9 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -5519,6 +6321,9 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E23" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -5541,12 +6346,65 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E24" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>COUNTIF(B26:E26, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -5557,7 +6415,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -5570,25 +6428,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5604,6 +6462,9 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -5626,6 +6487,9 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -5648,6 +6512,9 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -5670,6 +6537,9 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -5692,6 +6562,9 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -5714,6 +6587,9 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -5736,6 +6612,9 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -5758,6 +6637,9 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -5780,6 +6662,9 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -5802,6 +6687,9 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -5824,6 +6712,9 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -5846,6 +6737,9 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -5868,6 +6762,9 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -5890,6 +6787,9 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -5912,6 +6812,9 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -5934,6 +6837,9 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E17" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -5956,6 +6862,9 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -5978,6 +6887,9 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -6000,6 +6912,9 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -6022,6 +6937,9 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -6044,6 +6962,9 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -6066,6 +6987,9 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E23" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -6088,12 +7012,65 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E24" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>COUNTIF(B26:E26, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -6104,7 +7081,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -6112,13 +7089,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6417,6 +7394,32 @@
       </c>
       <c r="C24" s="5">
         <f>SUM('Week 1:Week 15'!H24) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="4">
+        <f>SUM('Week 1:Week 15'!H25)</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="5">
+        <f>SUM('Week 1:Week 15'!H25) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="4">
+        <f>SUM('Week 1:Week 15'!H26)</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="5">
+        <f>SUM('Week 1:Week 15'!H26) / 16</f>
         <v>0</v>
       </c>
     </row>
@@ -6427,7 +7430,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -6440,25 +7443,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6472,7 +7475,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
       </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
@@ -6488,12 +7494,15 @@
         <v>18</v>
       </c>
       <c r="B3" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="3" t="b">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="b">
         <v>0</v>
       </c>
       <c r="G3" s="4">
@@ -6518,6 +7527,9 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -6535,9 +7547,12 @@
         <v>0</v>
       </c>
       <c r="C5" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="b">
         <v>0</v>
       </c>
       <c r="G5" s="4">
@@ -6562,6 +7577,9 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -6584,6 +7602,9 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -6601,9 +7622,12 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="b">
         <v>0</v>
       </c>
       <c r="G8" s="4">
@@ -6628,6 +7652,9 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -6650,6 +7677,9 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -6672,6 +7702,9 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -6694,6 +7727,9 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -6716,6 +7752,9 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -6738,6 +7777,9 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -6760,6 +7802,9 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -6782,6 +7827,9 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -6804,6 +7852,9 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E17" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -6826,6 +7877,9 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -6848,6 +7902,9 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -6870,6 +7927,9 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -6884,12 +7944,15 @@
         <v>36</v>
       </c>
       <c r="B21" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="b">
         <v>0</v>
       </c>
       <c r="G21" s="4">
@@ -6914,6 +7977,9 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -6936,6 +8002,9 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E23" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -6958,12 +8027,65 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E24" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>COUNTIF(B26:E26, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -6974,7 +8096,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -6987,25 +8109,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7021,6 +8143,9 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -7043,6 +8168,9 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -7065,6 +8193,9 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -7087,6 +8218,9 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -7109,6 +8243,9 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -7131,6 +8268,9 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -7153,6 +8293,9 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -7175,6 +8318,9 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -7197,6 +8343,9 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -7219,6 +8368,9 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -7241,6 +8393,9 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -7263,6 +8418,9 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -7285,6 +8443,9 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -7307,6 +8468,9 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -7329,6 +8493,9 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -7351,6 +8518,9 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E17" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -7373,6 +8543,9 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -7395,6 +8568,9 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -7417,6 +8593,9 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -7439,6 +8618,9 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -7461,6 +8643,9 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -7483,6 +8668,9 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E23" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -7505,12 +8693,65 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E24" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>COUNTIF(B26:E26, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -7521,7 +8762,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -7534,25 +8775,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7568,6 +8809,9 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -7590,6 +8834,9 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -7612,6 +8859,9 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -7634,6 +8884,9 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -7656,6 +8909,9 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -7678,6 +8934,9 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -7700,6 +8959,9 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -7722,6 +8984,9 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -7744,6 +9009,9 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -7766,6 +9034,9 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -7788,6 +9059,9 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -7810,6 +9084,9 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -7832,6 +9109,9 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -7854,6 +9134,9 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -7876,6 +9159,9 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -7898,6 +9184,9 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E17" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -7920,6 +9209,9 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -7942,6 +9234,9 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -7964,6 +9259,9 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -7986,6 +9284,9 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -8008,6 +9309,9 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -8030,6 +9334,9 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E23" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -8052,12 +9359,65 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E24" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>COUNTIF(B26:E26, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -8068,7 +9428,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -8081,25 +9441,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8115,6 +9475,9 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -8137,6 +9500,9 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -8159,6 +9525,9 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -8181,6 +9550,9 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -8203,6 +9575,9 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -8225,6 +9600,9 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -8247,6 +9625,9 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -8269,6 +9650,9 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -8291,6 +9675,9 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -8313,6 +9700,9 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -8335,6 +9725,9 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -8357,6 +9750,9 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -8379,6 +9775,9 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -8401,6 +9800,9 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -8423,6 +9825,9 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -8445,6 +9850,9 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E17" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -8467,6 +9875,9 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -8489,6 +9900,9 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -8511,6 +9925,9 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -8533,6 +9950,9 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -8555,6 +9975,9 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -8577,6 +10000,9 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E23" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -8599,12 +10025,65 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E24" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>COUNTIF(B26:E26, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -8615,7 +10094,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -8628,25 +10107,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8662,6 +10141,9 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -8684,6 +10166,9 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -8706,6 +10191,9 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -8728,6 +10216,9 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -8750,6 +10241,9 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -8772,6 +10266,9 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -8794,6 +10291,9 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -8816,6 +10316,9 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -8838,6 +10341,9 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -8860,6 +10366,9 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -8882,6 +10391,9 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -8904,6 +10416,9 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -8926,6 +10441,9 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -8948,6 +10466,9 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -8970,6 +10491,9 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -8992,6 +10516,9 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E17" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -9014,6 +10541,9 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -9036,6 +10566,9 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -9058,6 +10591,9 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -9080,6 +10616,9 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -9102,6 +10641,9 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -9124,6 +10666,9 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E23" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -9146,12 +10691,65 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E24" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>COUNTIF(B26:E26, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -9162,7 +10760,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -9175,25 +10773,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -9209,6 +10807,9 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -9231,6 +10832,9 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -9253,6 +10857,9 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -9275,6 +10882,9 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -9297,6 +10907,9 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -9319,6 +10932,9 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -9341,6 +10957,9 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -9363,6 +10982,9 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -9385,6 +11007,9 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -9407,6 +11032,9 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -9429,6 +11057,9 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -9451,6 +11082,9 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -9473,6 +11107,9 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -9495,6 +11132,9 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -9517,6 +11157,9 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -9539,6 +11182,9 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E17" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -9561,6 +11207,9 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -9583,6 +11232,9 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -9605,6 +11257,9 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -9627,6 +11282,9 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -9649,6 +11307,9 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -9671,6 +11332,9 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E23" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -9693,12 +11357,65 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E24" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>COUNTIF(B26:E26, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -9709,7 +11426,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -9722,25 +11439,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -9756,6 +11473,9 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -9778,6 +11498,9 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -9800,6 +11523,9 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -9822,6 +11548,9 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -9844,6 +11573,9 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -9866,6 +11598,9 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -9888,6 +11623,9 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -9910,6 +11648,9 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -9932,6 +11673,9 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -9954,6 +11698,9 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -9976,6 +11723,9 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -9998,6 +11748,9 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -10020,6 +11773,9 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -10042,6 +11798,9 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -10064,6 +11823,9 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -10086,6 +11848,9 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E17" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -10108,6 +11873,9 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -10130,6 +11898,9 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -10152,6 +11923,9 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -10174,6 +11948,9 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -10196,6 +11973,9 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -10218,6 +11998,9 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E23" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -10240,12 +12023,65 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E24" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>COUNTIF(B26:E26, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -10256,7 +12092,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -10269,25 +12105,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -10303,6 +12139,9 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E2" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -10325,6 +12164,9 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -10347,6 +12189,9 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -10369,6 +12214,9 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E5" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -10391,6 +12239,9 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -10413,6 +12264,9 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E7" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -10435,6 +12289,9 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -10457,6 +12314,9 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -10479,6 +12339,9 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -10501,6 +12364,9 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E11" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -10523,6 +12389,9 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -10545,6 +12414,9 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E13" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -10567,6 +12439,9 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -10589,6 +12464,9 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -10611,6 +12489,9 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -10633,6 +12514,9 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E17" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -10655,6 +12539,9 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E18" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -10677,6 +12564,9 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E19" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -10699,6 +12589,9 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E20" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -10721,6 +12614,9 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E21" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -10743,6 +12639,9 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -10765,6 +12664,9 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E23" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -10787,12 +12689,65 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="E24" s="3" t="b">
+        <v>0</v>
+      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>COUNTIF(B26:E26, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="4">
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>

--- a/Attendance Tabloid.xlsx
+++ b/Attendance Tabloid.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="50">
   <si>
     <t>Name</t>
   </si>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>Bingham, Kenye'</t>
-  </si>
-  <si>
-    <t>Brown, Trinity</t>
   </si>
   <si>
     <t>Butler, Malachi</t>
@@ -218,7 +215,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC9DAF8"/>
+        <fgColor rgb="FFD0E0E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -2328,77 +2325,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
-      <c r="A26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="2">
-        <f>'Week 1'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="C26" s="2">
-        <f>'Week 2'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="2">
-        <f>'Week 3'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="2">
-        <f>'Week 4'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="2">
-        <f>'Week 5'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="2">
-        <f>'Week 6'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="2">
-        <f>'Week 7'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <f>'Week 8'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="2">
-        <f>'Week 9'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="2">
-        <f>'Week 10'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="L26" s="2">
-        <f>'Week 11'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="M26" s="2">
-        <f>'Week 12'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="N26" s="2">
-        <f>'Week 13'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="O26" s="2">
-        <f>'Week 14'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="P26" s="2">
-        <f>'Week 15'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="2">
-        <f>SUM(B26:P26)</f>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P26">
+  <conditionalFormatting sqref="B2:P25">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -2419,7 +2347,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -2432,25 +2360,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2466,9 +2394,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -2491,9 +2416,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -2516,9 +2438,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -2541,9 +2460,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -2566,9 +2482,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -2591,9 +2504,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -2616,9 +2526,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -2641,9 +2548,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -2666,9 +2570,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -2691,9 +2592,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -2716,9 +2614,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -2741,9 +2636,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -2766,9 +2658,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -2791,9 +2680,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -2816,9 +2702,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -2841,9 +2724,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -2866,9 +2746,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -2891,9 +2768,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -2916,9 +2790,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -2941,9 +2812,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -2966,9 +2834,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -2991,9 +2856,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -3016,9 +2878,6 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
@@ -3041,40 +2900,12 @@
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G25" s="4">
         <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3085,7 +2916,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -3098,25 +2929,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3132,9 +2963,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -3157,9 +2985,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -3182,9 +3007,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -3207,9 +3029,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -3232,9 +3051,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -3257,9 +3073,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -3282,9 +3095,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -3307,9 +3117,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -3332,9 +3139,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -3357,9 +3161,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -3382,9 +3183,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -3407,9 +3205,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -3432,9 +3227,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -3457,9 +3249,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -3482,9 +3271,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -3507,9 +3293,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -3532,9 +3315,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -3557,9 +3337,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -3582,9 +3359,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -3607,9 +3381,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -3632,9 +3403,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -3657,9 +3425,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -3682,9 +3447,6 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
@@ -3707,40 +3469,12 @@
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G25" s="4">
         <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3751,7 +3485,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -3764,25 +3498,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3798,9 +3532,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -3823,9 +3554,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -3848,9 +3576,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -3873,9 +3598,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -3898,9 +3620,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -3923,9 +3642,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -3948,9 +3664,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -3973,9 +3686,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -3998,9 +3708,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -4023,9 +3730,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -4048,9 +3752,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -4073,9 +3774,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -4098,9 +3796,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -4123,9 +3818,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -4148,9 +3840,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -4173,9 +3862,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -4198,9 +3884,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -4223,9 +3906,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -4248,9 +3928,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -4273,9 +3950,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -4298,9 +3972,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -4323,9 +3994,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -4348,9 +4016,6 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
@@ -4373,40 +4038,12 @@
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G25" s="4">
         <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -4417,7 +4054,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -4430,25 +4067,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4464,9 +4101,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -4489,9 +4123,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -4514,9 +4145,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -4539,9 +4167,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -4564,9 +4189,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -4589,9 +4211,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -4614,9 +4233,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -4639,9 +4255,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -4664,9 +4277,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -4689,9 +4299,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -4714,9 +4321,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -4739,9 +4343,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -4764,9 +4365,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -4789,9 +4387,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -4814,9 +4409,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -4839,9 +4431,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -4864,9 +4453,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -4889,9 +4475,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -4914,9 +4497,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -4939,9 +4519,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -4964,9 +4541,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -4989,9 +4563,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -5014,9 +4585,6 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
@@ -5039,40 +4607,12 @@
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G25" s="4">
         <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -5083,7 +4623,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -5096,25 +4636,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5130,9 +4670,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -5155,9 +4692,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -5180,9 +4714,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -5205,9 +4736,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -5230,9 +4758,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -5255,9 +4780,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -5280,9 +4802,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -5305,9 +4824,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -5330,9 +4846,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -5355,9 +4868,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -5380,9 +4890,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -5405,9 +4912,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -5430,9 +4934,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -5455,9 +4956,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -5480,9 +4978,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -5505,9 +5000,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -5530,9 +5022,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -5555,9 +5044,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -5580,9 +5066,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -5605,9 +5088,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -5630,9 +5110,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -5655,9 +5132,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -5680,9 +5154,6 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
@@ -5705,40 +5176,12 @@
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G25" s="4">
         <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -5749,7 +5192,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -5762,25 +5205,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5796,9 +5239,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -5821,9 +5261,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -5846,9 +5283,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -5871,9 +5305,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -5896,9 +5327,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -5921,9 +5349,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -5946,9 +5371,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -5971,9 +5393,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -5996,9 +5415,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -6021,9 +5437,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -6046,9 +5459,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -6071,9 +5481,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -6096,9 +5503,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -6121,9 +5525,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -6146,9 +5547,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -6171,9 +5569,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -6196,9 +5591,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -6221,9 +5613,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -6246,9 +5635,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -6271,9 +5657,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -6296,9 +5679,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -6321,9 +5701,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -6346,9 +5723,6 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
@@ -6371,40 +5745,12 @@
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G25" s="4">
         <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -6415,7 +5761,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -6428,25 +5774,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6462,9 +5808,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -6487,9 +5830,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -6512,9 +5852,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -6537,9 +5874,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -6562,9 +5896,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -6587,9 +5918,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -6612,9 +5940,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -6637,9 +5962,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -6662,9 +5984,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -6687,9 +6006,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -6712,9 +6028,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -6737,9 +6050,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -6762,9 +6072,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -6787,9 +6094,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -6812,9 +6116,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -6837,9 +6138,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -6862,9 +6160,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -6887,9 +6182,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -6912,9 +6204,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -6937,9 +6226,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -6962,9 +6248,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -6987,9 +6270,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -7012,9 +6292,6 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
@@ -7037,40 +6314,12 @@
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G25" s="4">
         <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -7081,7 +6330,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -7089,13 +6338,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -7407,19 +6656,6 @@
       </c>
       <c r="C25" s="5">
         <f>SUM('Week 1:Week 15'!H25) / 16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="4">
-        <f>SUM('Week 1:Week 15'!H26)</f>
-        <v>0</v>
-      </c>
-      <c r="C26" s="5">
-        <f>SUM('Week 1:Week 15'!H26) / 16</f>
         <v>0</v>
       </c>
     </row>
@@ -7430,7 +6666,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -7443,25 +6679,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7477,9 +6713,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -7502,9 +6735,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -7527,9 +6757,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -7552,9 +6779,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -7577,9 +6801,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -7602,9 +6823,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -7627,9 +6845,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -7652,9 +6867,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -7677,9 +6889,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -7702,9 +6911,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -7727,9 +6933,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -7752,9 +6955,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -7777,9 +6977,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -7802,9 +6999,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -7827,9 +7021,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -7852,9 +7043,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -7877,9 +7065,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -7902,9 +7087,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -7927,9 +7109,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -7952,9 +7131,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -7977,9 +7153,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -8002,9 +7175,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -8027,9 +7197,6 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
@@ -8052,40 +7219,12 @@
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G25" s="4">
         <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -8096,7 +7235,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -8109,25 +7248,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8143,9 +7282,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -8168,9 +7304,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -8193,9 +7326,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -8218,9 +7348,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -8243,9 +7370,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -8268,9 +7392,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -8293,9 +7414,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -8318,9 +7436,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -8343,9 +7458,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -8368,9 +7480,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -8393,9 +7502,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -8418,9 +7524,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -8443,9 +7546,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -8468,9 +7568,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -8493,9 +7590,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -8518,9 +7612,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -8543,9 +7634,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -8568,9 +7656,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -8593,9 +7678,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -8618,9 +7700,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -8643,9 +7722,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -8668,9 +7744,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -8693,9 +7766,6 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
@@ -8718,40 +7788,12 @@
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G25" s="4">
         <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -8762,7 +7804,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -8775,25 +7817,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8809,9 +7851,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -8834,9 +7873,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -8859,9 +7895,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -8884,9 +7917,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -8909,9 +7939,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -8934,9 +7961,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -8959,9 +7983,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -8984,9 +8005,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -9009,9 +8027,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -9034,9 +8049,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -9059,9 +8071,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -9084,9 +8093,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -9109,9 +8115,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -9134,9 +8137,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -9159,9 +8159,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -9184,9 +8181,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -9209,9 +8203,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -9234,9 +8225,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -9259,9 +8247,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -9284,9 +8269,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -9309,9 +8291,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -9334,9 +8313,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -9359,9 +8335,6 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
@@ -9384,40 +8357,12 @@
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G25" s="4">
         <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -9428,7 +8373,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -9441,25 +8386,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -9475,9 +8420,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -9500,9 +8442,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -9525,9 +8464,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -9550,9 +8486,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -9575,9 +8508,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -9600,9 +8530,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -9625,9 +8552,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -9650,9 +8574,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -9675,9 +8596,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -9700,9 +8618,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -9725,9 +8640,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -9750,9 +8662,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -9775,9 +8684,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -9800,9 +8706,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -9825,9 +8728,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -9850,9 +8750,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -9875,9 +8772,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -9900,9 +8794,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -9925,9 +8816,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -9950,9 +8838,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -9975,9 +8860,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -10000,9 +8882,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -10025,9 +8904,6 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
@@ -10050,40 +8926,12 @@
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G25" s="4">
         <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -10094,7 +8942,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -10107,25 +8955,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -10141,9 +8989,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -10166,9 +9011,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -10191,9 +9033,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -10216,9 +9055,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -10241,9 +9077,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -10266,9 +9099,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -10291,9 +9121,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -10316,9 +9143,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -10341,9 +9165,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -10366,9 +9187,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -10391,9 +9209,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -10416,9 +9231,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -10441,9 +9253,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -10466,9 +9275,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -10491,9 +9297,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -10516,9 +9319,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -10541,9 +9341,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -10566,9 +9363,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -10591,9 +9385,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -10616,9 +9407,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -10641,9 +9429,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -10666,9 +9451,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -10691,9 +9473,6 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
@@ -10716,40 +9495,12 @@
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G25" s="4">
         <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -10760,7 +9511,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -10773,25 +9524,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -10807,9 +9558,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -10832,9 +9580,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -10857,9 +9602,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -10882,9 +9624,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -10907,9 +9646,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -10932,9 +9668,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -10957,9 +9690,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -10982,9 +9712,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -11007,9 +9734,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -11032,9 +9756,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -11057,9 +9778,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -11082,9 +9800,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -11107,9 +9822,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -11132,9 +9844,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -11157,9 +9866,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -11182,9 +9888,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -11207,9 +9910,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -11232,9 +9932,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -11257,9 +9954,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -11282,9 +9976,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -11307,9 +9998,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -11332,9 +10020,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -11357,9 +10042,6 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
@@ -11382,40 +10064,12 @@
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G25" s="4">
         <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -11426,7 +10080,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -11439,25 +10093,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -11473,9 +10127,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -11498,9 +10149,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -11523,9 +10171,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -11548,9 +10193,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -11573,9 +10215,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -11598,9 +10237,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -11623,9 +10259,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -11648,9 +10281,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -11673,9 +10303,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -11698,9 +10325,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -11723,9 +10347,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -11748,9 +10369,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -11773,9 +10391,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -11798,9 +10413,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -11823,9 +10435,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -11848,9 +10457,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -11873,9 +10479,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -11898,9 +10501,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -11923,9 +10523,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -11948,9 +10545,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -11973,9 +10567,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -11998,9 +10589,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -12023,9 +10611,6 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
@@ -12048,40 +10633,12 @@
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G25" s="4">
         <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -12092,7 +10649,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -12105,25 +10662,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -12139,9 +10696,6 @@
       <c r="D2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
         <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
@@ -12164,9 +10718,6 @@
       <c r="D3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G3" s="4">
         <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
@@ -12189,9 +10740,6 @@
       <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G4" s="4">
         <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
@@ -12214,9 +10762,6 @@
       <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
         <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
@@ -12239,9 +10784,6 @@
       <c r="D6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
         <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
@@ -12264,9 +10806,6 @@
       <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
         <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
@@ -12289,9 +10828,6 @@
       <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G8" s="4">
         <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
@@ -12314,9 +10850,6 @@
       <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G9" s="4">
         <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
@@ -12339,9 +10872,6 @@
       <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
         <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
@@ -12364,9 +10894,6 @@
       <c r="D11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
         <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
@@ -12389,9 +10916,6 @@
       <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G12" s="4">
         <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
@@ -12414,9 +10938,6 @@
       <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
         <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
@@ -12439,9 +10960,6 @@
       <c r="D14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G14" s="4">
         <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
@@ -12464,9 +10982,6 @@
       <c r="D15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
         <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
@@ -12489,9 +11004,6 @@
       <c r="D16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G16" s="4">
         <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
@@ -12514,9 +11026,6 @@
       <c r="D17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G17" s="4">
         <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
@@ -12539,9 +11048,6 @@
       <c r="D18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G18" s="4">
         <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
@@ -12564,9 +11070,6 @@
       <c r="D19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G19" s="4">
         <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
@@ -12589,9 +11092,6 @@
       <c r="D20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G20" s="4">
         <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
@@ -12614,9 +11114,6 @@
       <c r="D21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E21" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G21" s="4">
         <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
@@ -12639,9 +11136,6 @@
       <c r="D22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G22" s="4">
         <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
@@ -12664,9 +11158,6 @@
       <c r="D23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G23" s="4">
         <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
@@ -12689,9 +11180,6 @@
       <c r="D24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G24" s="4">
         <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
@@ -12714,40 +11202,12 @@
       <c r="D25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E25" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G25" s="4">
         <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>

--- a/Attendance Tabloid.xlsx
+++ b/Attendance Tabloid.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="50">
   <si>
     <t>Name</t>
   </si>
@@ -81,6 +81,60 @@
   </si>
   <si>
     <t>Total Attended</t>
+  </si>
+  <si>
+    <t>Adegoke, Olusegun</t>
+  </si>
+  <si>
+    <t>Adeleye, Rasheed</t>
+  </si>
+  <si>
+    <t>babalola, paul</t>
+  </si>
+  <si>
+    <t>Beer, Colin</t>
+  </si>
+  <si>
+    <t>Bingham, Kenye'</t>
+  </si>
+  <si>
+    <t>Butler, Malachi</t>
+  </si>
+  <si>
+    <t>Cranor, Christian</t>
+  </si>
+  <si>
+    <t>Crenshaw, Makayla</t>
+  </si>
+  <si>
+    <t>Deckard, Jack</t>
+  </si>
+  <si>
+    <t>Diallo, Mohammad</t>
+  </si>
+  <si>
+    <t>Elliott, John</t>
+  </si>
+  <si>
+    <t>Femi-Ogunyemi, Judah</t>
+  </si>
+  <si>
+    <t>Guzman, Dayanara</t>
+  </si>
+  <si>
+    <t>Howe, Daniel</t>
+  </si>
+  <si>
+    <t>Jones, Larry</t>
+  </si>
+  <si>
+    <t>Kelly, Floyd</t>
+  </si>
+  <si>
+    <t>Krzywicki, Ryland</t>
+  </si>
+  <si>
+    <t>Maarouf, Ilyass</t>
   </si>
   <si>
     <t>Mellado Ostolaza, Johnny</t>
@@ -554,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -1029,8 +1083,1250 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2">
+        <f>'Week 1'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <f>'Week 2'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <f>'Week 3'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <f>'Week 4'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <f>'Week 5'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <f>'Week 6'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <f>'Week 7'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <f>'Week 8'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <f>'Week 9'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <f>'Week 10'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <f>'Week 11'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <f>'Week 12'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
+        <f>'Week 13'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="2">
+        <f>'Week 14'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
+        <f>'Week 15'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2">
+        <f>SUM(B8:P8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2">
+        <f>'Week 1'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <f>'Week 2'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <f>'Week 3'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <f>'Week 4'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <f>'Week 5'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <f>'Week 6'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <f>'Week 7'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <f>'Week 8'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <f>'Week 9'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <f>'Week 10'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="2">
+        <f>'Week 11'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <f>'Week 12'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
+        <f>'Week 13'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="2">
+        <f>'Week 14'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
+        <f>'Week 15'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2">
+        <f>SUM(B9:P9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2">
+        <f>'Week 1'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <f>'Week 2'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <f>'Week 3'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <f>'Week 4'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <f>'Week 5'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <f>'Week 6'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <f>'Week 7'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <f>'Week 8'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <f>'Week 9'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="2">
+        <f>'Week 10'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
+        <f>'Week 11'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
+        <f>'Week 12'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="2">
+        <f>'Week 13'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="2">
+        <f>'Week 14'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="P10" s="2">
+        <f>'Week 15'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2">
+        <f>SUM(B10:P10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="2">
+        <f>'Week 1'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <f>'Week 2'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <f>'Week 3'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <f>'Week 4'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <f>'Week 5'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <f>'Week 6'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <f>'Week 7'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <f>'Week 8'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <f>'Week 9'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
+        <f>'Week 10'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <f>'Week 11'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="2">
+        <f>'Week 12'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="2">
+        <f>'Week 13'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="2">
+        <f>'Week 14'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="2">
+        <f>'Week 15'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
+        <f>SUM(B11:P11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="2">
+        <f>'Week 1'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <f>'Week 2'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <f>'Week 3'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <f>'Week 4'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <f>'Week 5'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <f>'Week 6'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <f>'Week 7'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <f>'Week 8'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <f>'Week 9'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="2">
+        <f>'Week 10'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="2">
+        <f>'Week 11'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <f>'Week 12'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="2">
+        <f>'Week 13'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="2">
+        <f>'Week 14'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="2">
+        <f>'Week 15'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2">
+        <f>SUM(B12:P12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="2">
+        <f>'Week 1'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <f>'Week 2'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <f>'Week 3'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <f>'Week 4'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <f>'Week 5'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <f>'Week 6'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <f>'Week 7'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <f>'Week 8'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <f>'Week 9'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <f>'Week 10'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <f>'Week 11'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <f>'Week 12'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="2">
+        <f>'Week 13'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="2">
+        <f>'Week 14'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="2">
+        <f>'Week 15'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2">
+        <f>SUM(B13:P13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="2">
+        <f>'Week 1'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <f>'Week 2'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <f>'Week 3'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <f>'Week 4'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <f>'Week 5'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <f>'Week 6'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <f>'Week 7'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <f>'Week 8'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <f>'Week 9'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="2">
+        <f>'Week 10'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="2">
+        <f>'Week 11'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="2">
+        <f>'Week 12'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="2">
+        <f>'Week 13'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="2">
+        <f>'Week 14'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="2">
+        <f>'Week 15'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2">
+        <f>SUM(B14:P14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="2">
+        <f>'Week 1'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <f>'Week 2'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <f>'Week 3'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <f>'Week 4'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <f>'Week 5'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <f>'Week 6'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <f>'Week 7'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <f>'Week 8'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <f>'Week 9'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="2">
+        <f>'Week 10'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="2">
+        <f>'Week 11'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="2">
+        <f>'Week 12'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="2">
+        <f>'Week 13'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="2">
+        <f>'Week 14'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="2">
+        <f>'Week 15'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2">
+        <f>SUM(B15:P15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="2">
+        <f>'Week 1'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <f>'Week 2'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <f>'Week 3'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <f>'Week 4'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <f>'Week 5'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <f>'Week 6'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <f>'Week 7'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <f>'Week 8'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
+        <f>'Week 9'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="2">
+        <f>'Week 10'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="2">
+        <f>'Week 11'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="2">
+        <f>'Week 12'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="2">
+        <f>'Week 13'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="2">
+        <f>'Week 14'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="2">
+        <f>'Week 15'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2">
+        <f>SUM(B16:P16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="2">
+        <f>'Week 1'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <f>'Week 2'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <f>'Week 3'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <f>'Week 4'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <f>'Week 5'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <f>'Week 6'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <f>'Week 7'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <f>'Week 8'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <f>'Week 9'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="2">
+        <f>'Week 10'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="2">
+        <f>'Week 11'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="2">
+        <f>'Week 12'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="2">
+        <f>'Week 13'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="2">
+        <f>'Week 14'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="2">
+        <f>'Week 15'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2">
+        <f>SUM(B17:P17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2">
+        <f>'Week 1'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <f>'Week 2'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <f>'Week 3'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <f>'Week 4'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <f>'Week 5'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <f>'Week 6'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <f>'Week 7'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <f>'Week 8'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <f>'Week 9'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="2">
+        <f>'Week 10'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="2">
+        <f>'Week 11'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <f>'Week 12'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="2">
+        <f>'Week 13'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="2">
+        <f>'Week 14'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="2">
+        <f>'Week 15'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2">
+        <f>SUM(B18:P18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="2">
+        <f>'Week 1'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <f>'Week 2'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <f>'Week 3'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <f>'Week 4'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <f>'Week 5'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <f>'Week 6'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <f>'Week 7'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <f>'Week 8'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
+        <f>'Week 9'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
+        <f>'Week 10'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="2">
+        <f>'Week 11'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="2">
+        <f>'Week 12'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="2">
+        <f>'Week 13'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="2">
+        <f>'Week 14'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="2">
+        <f>'Week 15'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2">
+        <f>SUM(B19:P19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="2">
+        <f>'Week 1'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <f>'Week 2'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <f>'Week 3'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <f>'Week 4'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <f>'Week 5'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <f>'Week 6'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <f>'Week 7'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <f>'Week 8'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
+        <f>'Week 9'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="2">
+        <f>'Week 10'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="2">
+        <f>'Week 11'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="2">
+        <f>'Week 12'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="2">
+        <f>'Week 13'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="2">
+        <f>'Week 14'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="2">
+        <f>'Week 15'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2">
+        <f>SUM(B20:P20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="2">
+        <f>'Week 1'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="2">
+        <f>'Week 2'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <f>'Week 3'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <f>'Week 4'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <f>'Week 5'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <f>'Week 6'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <f>'Week 7'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <f>'Week 8'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <f>'Week 9'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
+        <f>'Week 10'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="2">
+        <f>'Week 11'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
+        <f>'Week 12'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
+        <f>'Week 13'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="2">
+        <f>'Week 14'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="P21" s="2">
+        <f>'Week 15'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2">
+        <f>SUM(B21:P21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="2">
+        <f>'Week 1'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <f>'Week 2'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <f>'Week 3'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <f>'Week 4'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <f>'Week 5'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <f>'Week 6'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <f>'Week 7'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <f>'Week 8'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
+        <f>'Week 9'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="2">
+        <f>'Week 10'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="2">
+        <f>'Week 11'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <f>'Week 12'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="2">
+        <f>'Week 13'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="O22" s="2">
+        <f>'Week 14'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="P22" s="2">
+        <f>'Week 15'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2">
+        <f>SUM(B22:P22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="2">
+        <f>'Week 1'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <f>'Week 2'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <f>'Week 3'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <f>'Week 4'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="2">
+        <f>'Week 5'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="2">
+        <f>'Week 6'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
+        <f>'Week 7'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <f>'Week 8'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
+        <f>'Week 9'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="2">
+        <f>'Week 10'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="2">
+        <f>'Week 11'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="2">
+        <f>'Week 12'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="2">
+        <f>'Week 13'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="O23" s="2">
+        <f>'Week 14'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="P23" s="2">
+        <f>'Week 15'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2">
+        <f>SUM(B23:P23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="2">
+        <f>'Week 1'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <f>'Week 2'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <f>'Week 3'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <f>'Week 4'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
+        <f>'Week 5'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
+        <f>'Week 6'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <f>'Week 7'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <f>'Week 8'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
+        <f>'Week 9'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="2">
+        <f>'Week 10'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="2">
+        <f>'Week 11'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="2">
+        <f>'Week 12'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="2">
+        <f>'Week 13'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="2">
+        <f>'Week 14'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="2">
+        <f>'Week 15'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2">
+        <f>SUM(B24:P24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="2">
+        <f>'Week 1'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <f>'Week 2'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <f>'Week 3'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="2">
+        <f>'Week 4'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <f>'Week 5'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <f>'Week 6'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <f>'Week 7'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <f>'Week 8'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
+        <f>'Week 9'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="2">
+        <f>'Week 10'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="2">
+        <f>'Week 11'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="2">
+        <f>'Week 12'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="N25" s="2">
+        <f>'Week 13'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="2">
+        <f>'Week 14'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="2">
+        <f>'Week 15'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2">
+        <f>SUM(B25:P25)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P7">
+  <conditionalFormatting sqref="B2:P25">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -1051,7 +2347,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -1064,25 +2360,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1214,6 +2510,402 @@
       </c>
       <c r="H7" s="4">
         <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(B8:E8, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <f>COUNTIF(B9:E9, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f>COUNTIF(B10:E10, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f>COUNTIF(B11:E11, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f>COUNTIF(B12:E12, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>COUNTIF(B13:E13, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>COUNTIF(B14:E14, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f>COUNTIF(B15:E15, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <f>COUNTIF(B16:E16, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIF(B17:E17, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIF(B18:E18, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIF(B19:E19, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(B20:E20, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(B21:E21, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIF(B22:E22, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIF(B23:E23, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIF(B24:E24, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -1224,7 +2916,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -1237,25 +2929,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1387,6 +3079,402 @@
       </c>
       <c r="H7" s="4">
         <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(B8:E8, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <f>COUNTIF(B9:E9, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f>COUNTIF(B10:E10, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f>COUNTIF(B11:E11, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f>COUNTIF(B12:E12, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>COUNTIF(B13:E13, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>COUNTIF(B14:E14, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f>COUNTIF(B15:E15, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <f>COUNTIF(B16:E16, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIF(B17:E17, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIF(B18:E18, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIF(B19:E19, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(B20:E20, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(B21:E21, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIF(B22:E22, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIF(B23:E23, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIF(B24:E24, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -1397,7 +3485,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -1410,25 +3498,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1560,6 +3648,402 @@
       </c>
       <c r="H7" s="4">
         <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(B8:E8, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <f>COUNTIF(B9:E9, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f>COUNTIF(B10:E10, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f>COUNTIF(B11:E11, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f>COUNTIF(B12:E12, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>COUNTIF(B13:E13, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>COUNTIF(B14:E14, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f>COUNTIF(B15:E15, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <f>COUNTIF(B16:E16, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIF(B17:E17, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIF(B18:E18, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIF(B19:E19, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(B20:E20, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(B21:E21, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIF(B22:E22, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIF(B23:E23, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIF(B24:E24, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -1570,7 +4054,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -1583,25 +4067,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1733,6 +4217,402 @@
       </c>
       <c r="H7" s="4">
         <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(B8:E8, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <f>COUNTIF(B9:E9, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f>COUNTIF(B10:E10, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f>COUNTIF(B11:E11, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f>COUNTIF(B12:E12, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>COUNTIF(B13:E13, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>COUNTIF(B14:E14, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f>COUNTIF(B15:E15, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <f>COUNTIF(B16:E16, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIF(B17:E17, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIF(B18:E18, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIF(B19:E19, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(B20:E20, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(B21:E21, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIF(B22:E22, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIF(B23:E23, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIF(B24:E24, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -1743,7 +4623,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -1756,25 +4636,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1906,6 +4786,402 @@
       </c>
       <c r="H7" s="4">
         <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(B8:E8, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <f>COUNTIF(B9:E9, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f>COUNTIF(B10:E10, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f>COUNTIF(B11:E11, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f>COUNTIF(B12:E12, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>COUNTIF(B13:E13, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>COUNTIF(B14:E14, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f>COUNTIF(B15:E15, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <f>COUNTIF(B16:E16, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIF(B17:E17, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIF(B18:E18, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIF(B19:E19, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(B20:E20, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(B21:E21, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIF(B22:E22, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIF(B23:E23, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIF(B24:E24, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -1916,7 +5192,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -1929,25 +5205,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2079,6 +5355,402 @@
       </c>
       <c r="H7" s="4">
         <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(B8:E8, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <f>COUNTIF(B9:E9, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f>COUNTIF(B10:E10, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f>COUNTIF(B11:E11, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f>COUNTIF(B12:E12, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>COUNTIF(B13:E13, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>COUNTIF(B14:E14, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f>COUNTIF(B15:E15, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <f>COUNTIF(B16:E16, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIF(B17:E17, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIF(B18:E18, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIF(B19:E19, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(B20:E20, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(B21:E21, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIF(B22:E22, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIF(B23:E23, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIF(B24:E24, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -2089,7 +5761,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -2102,25 +5774,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2252,6 +5924,402 @@
       </c>
       <c r="H7" s="4">
         <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(B8:E8, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <f>COUNTIF(B9:E9, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f>COUNTIF(B10:E10, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f>COUNTIF(B11:E11, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f>COUNTIF(B12:E12, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>COUNTIF(B13:E13, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>COUNTIF(B14:E14, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f>COUNTIF(B15:E15, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <f>COUNTIF(B16:E16, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIF(B17:E17, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIF(B18:E18, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIF(B19:E19, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(B20:E20, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(B21:E21, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIF(B22:E22, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIF(B23:E23, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIF(B24:E24, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -2262,7 +6330,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -2270,13 +6338,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2354,6 +6422,240 @@
       </c>
       <c r="C7" s="5">
         <f>SUM('Week 1:Week 15'!H7) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="4">
+        <f>SUM('Week 1:Week 15'!H8)</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="5">
+        <f>SUM('Week 1:Week 15'!H8) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="4">
+        <f>SUM('Week 1:Week 15'!H9)</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="5">
+        <f>SUM('Week 1:Week 15'!H9) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="4">
+        <f>SUM('Week 1:Week 15'!H10)</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="5">
+        <f>SUM('Week 1:Week 15'!H10) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="4">
+        <f>SUM('Week 1:Week 15'!H11)</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <f>SUM('Week 1:Week 15'!H11) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="4">
+        <f>SUM('Week 1:Week 15'!H12)</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="5">
+        <f>SUM('Week 1:Week 15'!H12) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="4">
+        <f>SUM('Week 1:Week 15'!H13)</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="5">
+        <f>SUM('Week 1:Week 15'!H13) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="4">
+        <f>SUM('Week 1:Week 15'!H14)</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="5">
+        <f>SUM('Week 1:Week 15'!H14) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="4">
+        <f>SUM('Week 1:Week 15'!H15)</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="5">
+        <f>SUM('Week 1:Week 15'!H15) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="4">
+        <f>SUM('Week 1:Week 15'!H16)</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="5">
+        <f>SUM('Week 1:Week 15'!H16) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="4">
+        <f>SUM('Week 1:Week 15'!H17)</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="5">
+        <f>SUM('Week 1:Week 15'!H17) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="4">
+        <f>SUM('Week 1:Week 15'!H18)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="5">
+        <f>SUM('Week 1:Week 15'!H18) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="4">
+        <f>SUM('Week 1:Week 15'!H19)</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="5">
+        <f>SUM('Week 1:Week 15'!H19) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="4">
+        <f>SUM('Week 1:Week 15'!H20)</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="5">
+        <f>SUM('Week 1:Week 15'!H20) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="4">
+        <f>SUM('Week 1:Week 15'!H21)</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="5">
+        <f>SUM('Week 1:Week 15'!H21) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="4">
+        <f>SUM('Week 1:Week 15'!H22)</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="5">
+        <f>SUM('Week 1:Week 15'!H22) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="4">
+        <f>SUM('Week 1:Week 15'!H23)</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="5">
+        <f>SUM('Week 1:Week 15'!H23) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="4">
+        <f>SUM('Week 1:Week 15'!H24)</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="5">
+        <f>SUM('Week 1:Week 15'!H24) / 16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="4">
+        <f>SUM('Week 1:Week 15'!H25)</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="5">
+        <f>SUM('Week 1:Week 15'!H25) / 16</f>
         <v>0</v>
       </c>
     </row>
@@ -2364,7 +6666,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -2377,25 +6679,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2527,6 +6829,402 @@
       </c>
       <c r="H7" s="4">
         <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(B8:E8, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <f>COUNTIF(B9:E9, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f>COUNTIF(B10:E10, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f>COUNTIF(B11:E11, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f>COUNTIF(B12:E12, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>COUNTIF(B13:E13, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>COUNTIF(B14:E14, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f>COUNTIF(B15:E15, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <f>COUNTIF(B16:E16, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIF(B17:E17, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIF(B18:E18, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIF(B19:E19, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(B20:E20, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(B21:E21, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIF(B22:E22, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIF(B23:E23, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIF(B24:E24, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -2537,7 +7235,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -2550,25 +7248,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2700,6 +7398,402 @@
       </c>
       <c r="H7" s="4">
         <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(B8:E8, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <f>COUNTIF(B9:E9, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f>COUNTIF(B10:E10, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f>COUNTIF(B11:E11, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f>COUNTIF(B12:E12, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>COUNTIF(B13:E13, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>COUNTIF(B14:E14, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f>COUNTIF(B15:E15, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <f>COUNTIF(B16:E16, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIF(B17:E17, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIF(B18:E18, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIF(B19:E19, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(B20:E20, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(B21:E21, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIF(B22:E22, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIF(B23:E23, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIF(B24:E24, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -2710,7 +7804,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -2723,25 +7817,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2873,6 +7967,402 @@
       </c>
       <c r="H7" s="4">
         <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(B8:E8, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <f>COUNTIF(B9:E9, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f>COUNTIF(B10:E10, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f>COUNTIF(B11:E11, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f>COUNTIF(B12:E12, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>COUNTIF(B13:E13, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>COUNTIF(B14:E14, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f>COUNTIF(B15:E15, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <f>COUNTIF(B16:E16, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIF(B17:E17, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIF(B18:E18, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIF(B19:E19, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(B20:E20, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(B21:E21, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIF(B22:E22, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIF(B23:E23, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIF(B24:E24, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -2883,7 +8373,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -2896,25 +8386,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3046,6 +8536,402 @@
       </c>
       <c r="H7" s="4">
         <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(B8:E8, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <f>COUNTIF(B9:E9, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f>COUNTIF(B10:E10, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f>COUNTIF(B11:E11, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f>COUNTIF(B12:E12, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>COUNTIF(B13:E13, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>COUNTIF(B14:E14, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f>COUNTIF(B15:E15, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <f>COUNTIF(B16:E16, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIF(B17:E17, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIF(B18:E18, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIF(B19:E19, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(B20:E20, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(B21:E21, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIF(B22:E22, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIF(B23:E23, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIF(B24:E24, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3056,7 +8942,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -3069,25 +8955,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3219,6 +9105,402 @@
       </c>
       <c r="H7" s="4">
         <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(B8:E8, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <f>COUNTIF(B9:E9, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f>COUNTIF(B10:E10, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f>COUNTIF(B11:E11, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f>COUNTIF(B12:E12, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>COUNTIF(B13:E13, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>COUNTIF(B14:E14, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f>COUNTIF(B15:E15, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <f>COUNTIF(B16:E16, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIF(B17:E17, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIF(B18:E18, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIF(B19:E19, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(B20:E20, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(B21:E21, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIF(B22:E22, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIF(B23:E23, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIF(B24:E24, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3229,7 +9511,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -3242,25 +9524,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3392,6 +9674,402 @@
       </c>
       <c r="H7" s="4">
         <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(B8:E8, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <f>COUNTIF(B9:E9, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f>COUNTIF(B10:E10, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f>COUNTIF(B11:E11, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f>COUNTIF(B12:E12, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>COUNTIF(B13:E13, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>COUNTIF(B14:E14, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f>COUNTIF(B15:E15, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <f>COUNTIF(B16:E16, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIF(B17:E17, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIF(B18:E18, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIF(B19:E19, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(B20:E20, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(B21:E21, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIF(B22:E22, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIF(B23:E23, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIF(B24:E24, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3402,7 +10080,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -3415,25 +10093,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3565,6 +10243,402 @@
       </c>
       <c r="H7" s="4">
         <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(B8:E8, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <f>COUNTIF(B9:E9, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f>COUNTIF(B10:E10, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f>COUNTIF(B11:E11, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f>COUNTIF(B12:E12, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>COUNTIF(B13:E13, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>COUNTIF(B14:E14, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f>COUNTIF(B15:E15, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <f>COUNTIF(B16:E16, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIF(B17:E17, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIF(B18:E18, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIF(B19:E19, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(B20:E20, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(B21:E21, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIF(B22:E22, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIF(B23:E23, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIF(B24:E24, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3575,7 +10649,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -3588,25 +10662,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3738,6 +10812,402 @@
       </c>
       <c r="H7" s="4">
         <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <f>COUNTIF(B8:E8, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <f>COUNTIF(B9:E9, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <f>COUNTIF(B10:E10, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <f>COUNTIF(B11:E11, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <f>COUNTIF(B12:E12, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>COUNTIF(B13:E13, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>COUNTIF(B14:E14, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <f>COUNTIF(B15:E15, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <f>COUNTIF(B16:E16, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <f>COUNTIF(B17:E17, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <f>COUNTIF(B18:E18, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <f>COUNTIF(B19:E19, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <f>COUNTIF(B20:E20, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <f>COUNTIF(B21:E21, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>COUNTIF(B22:E22, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>COUNTIF(B23:E23, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>COUNTIF(B24:E24, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>COUNTIF(B25:E25, TRUE)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="4">
+        <f>COUNTIF(C25, TRUE)</f>
         <v>0</v>
       </c>
     </row>

--- a/Attendance Tabloid.xlsx
+++ b/Attendance Tabloid.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\butlemal\Desktop\PyTendance\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11B53A1-44EC-4F33-83FC-FC8B158D308E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4575" windowWidth="28005" windowHeight="12645" firstSheet="6" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -31,20 +25,7 @@
     <sheet name="Week 15" sheetId="16" r:id="rId16"/>
     <sheet name="Total Labs Attended" sheetId="17" r:id="rId17"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -186,13 +167,13 @@
     <t>Names</t>
   </si>
   <si>
-    <t>Tuesday Lecture</t>
+    <t>Monday Lecture</t>
   </si>
   <si>
-    <t>Tuesday Lab</t>
+    <t>Monday Lab</t>
   </si>
   <si>
-    <t>Thursday Lecture</t>
+    <t>Wednesday Lecture</t>
   </si>
   <si>
     <t>Attended Help Session?</t>
@@ -207,8 +188,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00%"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,7 +218,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6B8AF"/>
+        <fgColor rgb="FFCFE2F3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -284,7 +268,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -295,7 +279,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFE599"/>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB7E1CD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -309,27 +300,12 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEA9999"/>
+          <bgColor rgb="FFFFE599"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -351,9 +327,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -391,7 +367,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -425,7 +401,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -460,10 +435,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -636,16 +610,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
     <col min="2" max="16" width="10.7109375" customWidth="1"/>
     <col min="17" max="17" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -698,7 +672,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -763,11 +737,11 @@
         <v>0</v>
       </c>
       <c r="Q2" s="2">
-        <f t="shared" ref="Q2:Q26" si="0">SUM(B2:P2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B2:P2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -832,11 +806,11 @@
         <v>0</v>
       </c>
       <c r="Q3" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B3:P3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -901,11 +875,11 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B4:P4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
@@ -970,11 +944,11 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B5:P5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -1039,11 +1013,11 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B6:P6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -1108,11 +1082,11 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B7:P7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -1177,11 +1151,11 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B8:P8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -1246,11 +1220,11 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B9:P9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
@@ -1315,11 +1289,11 @@
         <v>0</v>
       </c>
       <c r="Q10" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B10:P10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -1384,11 +1358,11 @@
         <v>0</v>
       </c>
       <c r="Q11" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B11:P11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="2" t="s">
         <v>27</v>
       </c>
@@ -1453,11 +1427,11 @@
         <v>0</v>
       </c>
       <c r="Q12" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B12:P12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
@@ -1522,11 +1496,11 @@
         <v>0</v>
       </c>
       <c r="Q13" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B13:P13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
@@ -1591,11 +1565,11 @@
         <v>0</v>
       </c>
       <c r="Q14" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B14:P14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
         <v>30</v>
       </c>
@@ -1660,11 +1634,11 @@
         <v>0</v>
       </c>
       <c r="Q15" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B15:P15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
@@ -1729,11 +1703,11 @@
         <v>0</v>
       </c>
       <c r="Q16" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B16:P16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
@@ -1798,11 +1772,11 @@
         <v>0</v>
       </c>
       <c r="Q17" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B17:P17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="2" t="s">
         <v>33</v>
       </c>
@@ -1867,11 +1841,11 @@
         <v>0</v>
       </c>
       <c r="Q18" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B18:P18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="2" t="s">
         <v>34</v>
       </c>
@@ -1936,11 +1910,11 @@
         <v>0</v>
       </c>
       <c r="Q19" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B19:P19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="2" t="s">
         <v>35</v>
       </c>
@@ -2005,11 +1979,11 @@
         <v>0</v>
       </c>
       <c r="Q20" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B20:P20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="2" t="s">
         <v>36</v>
       </c>
@@ -2074,11 +2048,11 @@
         <v>0</v>
       </c>
       <c r="Q21" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B21:P21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="2" t="s">
         <v>37</v>
       </c>
@@ -2143,11 +2117,11 @@
         <v>0</v>
       </c>
       <c r="Q22" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B22:P22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" s="2" t="s">
         <v>38</v>
       </c>
@@ -2212,11 +2186,11 @@
         <v>0</v>
       </c>
       <c r="Q23" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B23:P23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24" s="2" t="s">
         <v>39</v>
       </c>
@@ -2281,11 +2255,11 @@
         <v>0</v>
       </c>
       <c r="Q24" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B24:P24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25" s="2" t="s">
         <v>40</v>
       </c>
@@ -2350,11 +2324,11 @@
         <v>0</v>
       </c>
       <c r="Q25" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+        <f>SUM(B25:P25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26" s="2" t="s">
         <v>41</v>
       </c>
@@ -2419,23 +2393,23 @@
         <v>0</v>
       </c>
       <c r="Q26" s="2">
-        <f t="shared" si="0"/>
+        <f>SUM(B26:P26)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:P26">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>1</formula>
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2444,19 +2418,19 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2479,7 +2453,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -2496,15 +2470,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -2521,15 +2495,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -2546,15 +2520,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -2571,15 +2545,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -2596,15 +2570,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2621,15 +2595,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -2646,15 +2620,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2671,15 +2645,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -2696,15 +2670,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -2721,15 +2695,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -2746,15 +2720,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2771,15 +2745,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -2796,15 +2770,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2821,15 +2795,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -2846,15 +2820,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -2871,15 +2845,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -2896,15 +2870,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -2921,15 +2895,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -2946,15 +2920,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -2971,15 +2945,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -2996,15 +2970,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -3021,15 +2995,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -3046,15 +3020,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -3071,15 +3045,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -3096,11 +3070,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3110,19 +3084,19 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3145,7 +3119,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -3162,15 +3136,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3187,15 +3161,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -3212,15 +3186,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -3237,15 +3211,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -3262,15 +3236,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3287,15 +3261,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -3312,15 +3286,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -3337,15 +3311,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -3362,15 +3336,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -3387,15 +3361,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -3412,15 +3386,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -3437,15 +3411,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -3462,15 +3436,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -3487,15 +3461,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -3512,15 +3486,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3537,15 +3511,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -3562,15 +3536,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -3587,15 +3561,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -3612,15 +3586,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -3637,15 +3611,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -3662,15 +3636,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -3687,15 +3661,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -3712,15 +3686,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -3737,15 +3711,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -3762,11 +3736,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3776,19 +3750,19 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3811,7 +3785,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -3828,15 +3802,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3853,15 +3827,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -3878,15 +3852,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -3903,15 +3877,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -3928,15 +3902,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3953,15 +3927,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -3978,15 +3952,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -4003,15 +3977,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -4028,15 +4002,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -4053,15 +4027,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -4078,15 +4052,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -4103,15 +4077,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -4128,15 +4102,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -4153,15 +4127,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -4178,15 +4152,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -4203,15 +4177,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -4228,15 +4202,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -4253,15 +4227,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -4278,15 +4252,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -4303,15 +4277,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -4328,15 +4302,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -4353,15 +4327,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -4378,15 +4352,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -4403,15 +4377,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -4428,11 +4402,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -4442,19 +4416,19 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4477,7 +4451,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -4494,15 +4468,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -4519,15 +4493,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -4544,15 +4518,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -4569,15 +4543,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -4594,15 +4568,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -4619,15 +4593,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -4644,15 +4618,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -4669,15 +4643,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -4694,15 +4668,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -4719,15 +4693,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -4744,15 +4718,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -4769,15 +4743,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -4794,15 +4768,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -4819,15 +4793,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -4844,15 +4818,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -4869,15 +4843,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -4894,15 +4868,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -4919,15 +4893,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -4944,15 +4918,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -4969,15 +4943,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -4994,15 +4968,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -5019,15 +4993,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -5044,15 +5018,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -5069,15 +5043,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -5094,11 +5068,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -5108,19 +5082,19 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5143,7 +5117,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -5160,15 +5134,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -5185,15 +5159,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -5210,15 +5184,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -5235,15 +5209,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -5260,15 +5234,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -5285,15 +5259,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -5310,15 +5284,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -5335,15 +5309,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -5360,15 +5334,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -5385,15 +5359,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -5410,15 +5384,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -5435,15 +5409,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -5460,15 +5434,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -5485,15 +5459,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -5510,15 +5484,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -5535,15 +5509,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -5560,15 +5534,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -5585,15 +5559,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -5610,15 +5584,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -5635,15 +5609,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -5660,15 +5634,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -5685,15 +5659,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -5710,15 +5684,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -5735,15 +5709,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -5760,11 +5734,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -5774,19 +5748,19 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5809,7 +5783,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -5826,15 +5800,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -5851,15 +5825,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -5876,15 +5850,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -5901,15 +5875,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -5926,15 +5900,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -5951,15 +5925,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -5976,15 +5950,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -6001,15 +5975,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -6026,15 +6000,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -6051,15 +6025,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -6076,15 +6050,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -6101,15 +6075,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -6126,15 +6100,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -6151,15 +6125,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -6176,15 +6150,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -6201,15 +6175,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -6226,15 +6200,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -6251,15 +6225,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -6276,15 +6250,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -6301,15 +6275,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -6326,15 +6300,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -6351,15 +6325,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -6376,15 +6350,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -6401,15 +6375,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -6426,11 +6400,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -6440,19 +6414,19 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -6475,7 +6449,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -6492,15 +6466,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -6517,15 +6491,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -6542,15 +6516,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -6567,15 +6541,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -6592,15 +6566,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -6617,15 +6591,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -6642,15 +6616,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -6667,15 +6641,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -6692,15 +6666,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -6717,15 +6691,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -6742,15 +6716,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -6767,15 +6741,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -6792,15 +6766,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -6817,15 +6791,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -6842,15 +6816,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -6867,15 +6841,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -6892,15 +6866,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -6917,15 +6891,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -6942,15 +6916,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -6967,15 +6941,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -6992,15 +6966,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -7017,15 +6991,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -7042,15 +7016,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -7067,15 +7041,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -7092,11 +7066,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -7106,14 +7080,14 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -7124,7 +7098,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -7137,7 +7111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -7150,7 +7124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -7163,7 +7137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -7176,7 +7150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -7189,7 +7163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -7202,7 +7176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -7215,7 +7189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -7228,7 +7202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -7241,7 +7215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -7254,7 +7228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -7267,7 +7241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -7280,7 +7254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -7293,7 +7267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -7306,7 +7280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -7319,7 +7293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -7332,7 +7306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -7345,7 +7319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -7358,7 +7332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -7371,7 +7345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -7384,7 +7358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -7397,7 +7371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -7410,7 +7384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -7423,7 +7397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -7436,7 +7410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -7455,19 +7429,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -7490,7 +7464,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -7507,15 +7481,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -7532,15 +7506,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -7557,15 +7531,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -7582,15 +7556,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -7607,15 +7581,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -7632,15 +7606,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -7657,15 +7631,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -7682,15 +7656,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -7707,15 +7681,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -7732,15 +7706,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -7757,15 +7731,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -7782,15 +7756,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -7807,15 +7781,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -7832,15 +7806,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -7857,15 +7831,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -7882,15 +7856,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -7907,15 +7881,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -7932,15 +7906,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -7957,15 +7931,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -7982,15 +7956,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -8007,15 +7981,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -8032,15 +8006,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -8057,15 +8031,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -8082,15 +8056,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -8107,11 +8081,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -8121,19 +8095,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -8156,7 +8130,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -8173,15 +8147,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -8198,15 +8172,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -8223,15 +8197,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -8248,15 +8222,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -8273,15 +8247,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -8298,15 +8272,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -8323,15 +8297,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -8348,15 +8322,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -8373,15 +8347,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -8398,15 +8372,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -8423,15 +8397,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -8448,15 +8422,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -8473,15 +8447,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -8498,15 +8472,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -8523,15 +8497,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -8548,15 +8522,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -8573,15 +8547,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -8598,15 +8572,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -8623,15 +8597,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -8648,15 +8622,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -8673,15 +8647,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -8698,15 +8672,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -8723,15 +8697,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -8748,15 +8722,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -8773,11 +8747,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -8787,19 +8761,19 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -8822,7 +8796,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -8839,15 +8813,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -8864,15 +8838,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -8889,15 +8863,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -8914,15 +8888,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -8939,15 +8913,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -8964,15 +8938,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -8989,15 +8963,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -9014,15 +8988,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -9039,15 +9013,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -9064,15 +9038,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -9089,15 +9063,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -9114,15 +9088,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -9139,15 +9113,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -9164,15 +9138,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -9189,15 +9163,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -9214,15 +9188,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -9239,15 +9213,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -9264,15 +9238,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -9289,15 +9263,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -9314,15 +9288,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -9339,15 +9313,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -9364,15 +9338,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -9389,15 +9363,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -9414,15 +9388,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -9439,11 +9413,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -9453,19 +9427,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -9488,7 +9462,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -9505,15 +9479,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -9530,15 +9504,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -9555,15 +9529,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -9580,15 +9554,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -9605,15 +9579,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -9630,15 +9604,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -9655,15 +9629,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -9680,15 +9654,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -9705,15 +9679,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -9730,15 +9704,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -9755,15 +9729,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -9780,15 +9754,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -9805,15 +9779,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -9830,15 +9804,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -9855,15 +9829,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -9880,15 +9854,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -9905,15 +9879,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -9930,15 +9904,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -9955,15 +9929,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -9980,15 +9954,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -10005,15 +9979,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -10030,15 +10004,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -10055,15 +10029,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -10080,15 +10054,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -10105,11 +10079,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -10119,19 +10093,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -10154,7 +10128,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -10171,15 +10145,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -10196,15 +10170,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -10221,15 +10195,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -10246,15 +10220,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -10271,15 +10245,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -10296,15 +10270,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -10321,15 +10295,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -10346,15 +10320,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -10371,15 +10345,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -10396,15 +10370,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -10421,15 +10395,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -10446,15 +10420,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -10471,15 +10445,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -10496,15 +10470,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -10521,15 +10495,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -10546,15 +10520,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -10571,15 +10545,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -10596,15 +10570,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -10621,15 +10595,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -10646,15 +10620,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -10671,15 +10645,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -10696,15 +10670,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -10721,15 +10695,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -10746,15 +10720,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -10771,11 +10745,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -10785,19 +10759,19 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -10820,7 +10794,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -10837,15 +10811,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -10862,15 +10836,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -10887,15 +10861,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -10912,15 +10886,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -10937,15 +10911,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -10962,15 +10936,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -10987,15 +10961,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -11012,15 +10986,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -11037,15 +11011,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -11062,15 +11036,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -11087,15 +11061,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -11112,15 +11086,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -11137,15 +11111,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -11162,15 +11136,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -11187,15 +11161,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -11212,15 +11186,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -11237,15 +11211,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -11262,15 +11236,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -11287,15 +11261,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -11312,15 +11286,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -11337,15 +11311,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -11362,15 +11336,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -11387,15 +11361,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -11412,15 +11386,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -11437,11 +11411,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -11451,19 +11425,19 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -11486,7 +11460,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -11503,15 +11477,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -11528,15 +11502,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -11553,15 +11527,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -11578,15 +11552,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -11603,15 +11577,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -11628,15 +11602,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -11653,15 +11627,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -11678,15 +11652,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -11703,15 +11677,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -11728,15 +11702,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -11753,15 +11727,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -11778,15 +11752,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -11803,15 +11777,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -11828,15 +11802,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -11853,15 +11827,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -11878,15 +11852,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -11903,15 +11877,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -11928,15 +11902,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -11953,15 +11927,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -11978,15 +11952,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -12003,15 +11977,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -12028,15 +12002,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -12053,15 +12027,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -12078,15 +12052,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -12103,11 +12077,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -12117,19 +12091,19 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -12152,7 +12126,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -12169,15 +12143,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G26" si="0">COUNTIF(B2:E2, TRUE)</f>
+        <f>COUNTIF(B2:E2, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <f t="shared" ref="H2:H26" si="1">COUNTIF(C2, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C2, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -12194,15 +12168,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B3:E3, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C3, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -12219,15 +12193,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B4:E4, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C4, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -12244,15 +12218,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B5:E5, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C5, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -12269,15 +12243,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B6:E6, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C6, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -12294,15 +12268,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B7:E7, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C7, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -12319,15 +12293,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B8:E8, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C8, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -12344,15 +12318,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B9:E9, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C9, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -12369,15 +12343,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B10:E10, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C10, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -12394,15 +12368,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B11:E11, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C11, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -12419,15 +12393,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B12:E12, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C12, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -12444,15 +12418,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B13:E13, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C13, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -12469,15 +12443,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B14:E14, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C14, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -12494,15 +12468,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B15:E15, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C15, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -12519,15 +12493,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B16:E16, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C16, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -12544,15 +12518,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B17:E17, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C17, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -12569,15 +12543,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B18:E18, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C18, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -12594,15 +12568,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B19:E19, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C19, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -12619,15 +12593,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B20:E20, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C20, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -12644,15 +12618,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B21:E21, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C21, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -12669,15 +12643,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B22:E22, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C22, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -12694,15 +12668,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B23:E23, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C23, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -12719,15 +12693,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B24:E24, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C24, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -12744,15 +12718,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B25:E25, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>COUNTIF(C25, TRUE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -12769,11 +12743,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(B26:E26, TRUE)</f>
         <v>0</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>

--- a/Attendance Tabloid.xlsx
+++ b/Attendance Tabloid.xlsx
@@ -89,7 +89,7 @@
     <t>Adeleye, Rasheed</t>
   </si>
   <si>
-    <t>babalola, paul</t>
+    <t>Babalola, Paul</t>
   </si>
   <si>
     <t>Beer, Colin</t>
@@ -167,13 +167,13 @@
     <t>Names</t>
   </si>
   <si>
-    <t>Monday Lecture</t>
+    <t>Tuesday Lecture</t>
   </si>
   <si>
-    <t>Monday Lab</t>
+    <t>Tuesday Lab</t>
   </si>
   <si>
-    <t>Wednesday Lecture</t>
+    <t>Thursday Lecture</t>
   </si>
   <si>
     <t>Attended Help Session?</t>
@@ -218,7 +218,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCFE2F3"/>
+        <fgColor rgb="FFD0E0E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2423,9 +2423,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
@@ -3089,9 +3089,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
@@ -3755,9 +3755,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
@@ -4421,9 +4421,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
@@ -5087,9 +5087,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
@@ -5753,9 +5753,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
@@ -6419,9 +6419,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
@@ -7434,9 +7434,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
@@ -8100,9 +8100,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
@@ -8766,9 +8766,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
@@ -9432,9 +9432,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
@@ -10098,9 +10098,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
@@ -10764,9 +10764,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
@@ -11430,9 +11430,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>
@@ -12096,9 +12096,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="8" width="18.7109375" customWidth="1"/>
   </cols>

--- a/Attendance Tabloid.xlsx
+++ b/Attendance Tabloid.xlsx
@@ -218,7 +218,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD0E0E3"/>
+        <fgColor rgb="FFFCE5CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>

--- a/Attendance Tabloid.xlsx
+++ b/Attendance Tabloid.xlsx
@@ -218,7 +218,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE5CD"/>
+        <fgColor rgb="FFF4CCCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>

--- a/Attendance Tabloid.xlsx
+++ b/Attendance Tabloid.xlsx
@@ -218,7 +218,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
+        <fgColor rgb="FFD9EAD3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>

--- a/Attendance Tabloid.xlsx
+++ b/Attendance Tabloid.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="50">
   <si>
     <t>Name</t>
   </si>
@@ -99,9 +99,6 @@
   </si>
   <si>
     <t>Brown, Trinity</t>
-  </si>
-  <si>
-    <t>Butler, Malachi</t>
   </si>
   <si>
     <t>Cranor, Christian</t>
@@ -218,7 +215,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="FFC9DAF8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -2328,77 +2325,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
-      <c r="A26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="2">
-        <f>'Week 1'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="C26" s="2">
-        <f>'Week 2'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="2">
-        <f>'Week 3'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="2">
-        <f>'Week 4'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="2">
-        <f>'Week 5'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="2">
-        <f>'Week 6'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="2">
-        <f>'Week 7'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <f>'Week 8'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="2">
-        <f>'Week 9'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="2">
-        <f>'Week 10'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="L26" s="2">
-        <f>'Week 11'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="M26" s="2">
-        <f>'Week 12'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="N26" s="2">
-        <f>'Week 13'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="O26" s="2">
-        <f>'Week 14'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="P26" s="2">
-        <f>'Week 15'!G26</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="2">
-        <f>SUM(B26:P26)</f>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P26">
+  <conditionalFormatting sqref="B2:P25">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -2419,7 +2347,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -2432,25 +2360,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3050,31 +2978,6 @@
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3085,7 +2988,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -3098,25 +3001,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3716,31 +3619,6 @@
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -3751,7 +3629,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -3764,25 +3642,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4382,31 +4260,6 @@
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -4417,7 +4270,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -4430,25 +4283,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5048,31 +4901,6 @@
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -5083,7 +4911,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -5096,25 +4924,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5714,31 +5542,6 @@
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -5749,7 +5552,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -5762,25 +5565,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6380,31 +6183,6 @@
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -6415,7 +6193,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -6428,25 +6206,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7046,31 +6824,6 @@
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -7081,7 +6834,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -7089,13 +6842,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -7407,19 +7160,6 @@
       </c>
       <c r="C25" s="5">
         <f>SUM('Week 1:Week 15'!H25) / 16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="4">
-        <f>SUM('Week 1:Week 15'!H26)</f>
-        <v>0</v>
-      </c>
-      <c r="C26" s="5">
-        <f>SUM('Week 1:Week 15'!H26) / 16</f>
         <v>0</v>
       </c>
     </row>
@@ -7430,7 +7170,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -7443,25 +7183,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7519,7 +7259,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="b">
         <v>0</v>
@@ -7544,7 +7284,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="b">
         <v>0</v>
@@ -7569,7 +7309,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="b">
         <v>0</v>
@@ -7594,7 +7334,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="3" t="b">
         <v>0</v>
@@ -7619,7 +7359,7 @@
         <v>23</v>
       </c>
       <c r="B8" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="3" t="b">
         <v>0</v>
@@ -8061,31 +7801,6 @@
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -8096,7 +7811,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -8109,25 +7824,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8727,31 +8442,6 @@
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -8762,7 +8452,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -8775,25 +8465,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -9393,31 +9083,6 @@
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -9428,7 +9093,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -9441,25 +9106,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -10059,31 +9724,6 @@
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -10094,7 +9734,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -10107,25 +9747,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -10725,31 +10365,6 @@
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -10760,7 +10375,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -10773,25 +10388,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -11391,31 +11006,6 @@
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -11426,7 +11016,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -11439,25 +11029,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -12057,31 +11647,6 @@
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -12092,7 +11657,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -12105,25 +11670,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -12723,31 +12288,6 @@
       </c>
       <c r="H25" s="4">
         <f>COUNTIF(C25, TRUE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f>COUNTIF(B26:E26, TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f>COUNTIF(C26, TRUE)</f>
         <v>0</v>
       </c>
     </row>

--- a/Attendance Tabloid.xlsx
+++ b/Attendance Tabloid.xlsx
@@ -218,7 +218,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="FFF4CCCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
